--- a/data/k-props/2026-08-16.xlsx
+++ b/data/k-props/2026-08-16.xlsx
@@ -133,25 +133,40 @@
     <t>08/16/2026</t>
   </si>
   <si>
+    <t>Trevor Rogers</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
     <t>Freddy Peralta</t>
   </si>
   <si>
-    <t>Baltimore Orioles @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Trevor Rogers</t>
+    <t>Patrick Sandoval</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Lake Bachar</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
   </si>
   <si>
     <t>Michael Soroka</t>
@@ -163,136 +178,121 @@
     <t>Bryce Elder</t>
   </si>
   <si>
-    <t>Patrick Sandoval</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Pittsburgh Pirates</t>
+    <t>Ryan Weathers</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Dylan Cease</t>
+  </si>
+  <si>
+    <t>Jake Irvin</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ New York Mets</t>
+  </si>
+  <si>
+    <t>Christian Scott</t>
+  </si>
+  <si>
+    <t>Casey Mize</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Tanner Bibee</t>
+  </si>
+  <si>
+    <t>Sean Burke</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Drew Anderson</t>
+  </si>
+  <si>
+    <t>Eury Pérez</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Nick Lodolo</t>
+  </si>
+  <si>
+    <t>Andrew Painter</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Dean Kremer</t>
+  </si>
+  <si>
+    <t>Hunter Dobbins</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Chicago Cubs</t>
   </si>
   <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t>Dylan Cease</t>
-  </si>
-  <si>
-    <t>New York Yankees @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Ryan Weathers</t>
-  </si>
-  <si>
-    <t>Drew Anderson</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Sean Burke</t>
+    <t>Edward Cabrera</t>
+  </si>
+  <si>
+    <t>Gabriel Hughes</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Blade Tidwell</t>
+  </si>
+  <si>
+    <t>Jacob Lopez</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Athletics</t>
+  </si>
+  <si>
+    <t>Noah Cameron</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Ryan Johnson</t>
+  </si>
+  <si>
+    <t>Logan Henderson</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Tarik Skubal</t>
+  </si>
+  <si>
+    <t>Bryan Woo</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Hunter Brown</t>
   </si>
   <si>
     <t>Eury Perez</t>
   </si>
   <si>
-    <t>Miami Marlins @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Nick Lodolo</t>
-  </si>
-  <si>
-    <t>Casey Mize</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Tanner Bibee</t>
-  </si>
-  <si>
-    <t>Jake Irvin</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ New York Mets</t>
-  </si>
-  <si>
-    <t>Christian Scott</t>
-  </si>
-  <si>
-    <t>Andrew Painter</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Dean Kremer</t>
-  </si>
-  <si>
-    <t>Hunter Dobbins</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Edward Cabrera</t>
-  </si>
-  <si>
-    <t>Blade Tidwell</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Gabriel Hughes</t>
-  </si>
-  <si>
     <t>Cody Bradford</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Athletics</t>
-  </si>
-  <si>
-    <t>Jacob Lopez</t>
-  </si>
-  <si>
-    <t>Noah Cameron</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Ryan Johnson</t>
-  </si>
-  <si>
-    <t>Tarik Skubal</t>
-  </si>
-  <si>
-    <t>Milwaukee Brewers @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Logan Henderson</t>
-  </si>
-  <si>
-    <t>Hunter Brown</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Bryan Woo</t>
-  </si>
-  <si>
-    <t>Lake Bachar</t>
-  </si>
-  <si>
-    <t>Eury Pérez</t>
   </si>
 </sst>
 </file>
@@ -806,13 +806,13 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D2">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E2">
-        <v>-148</v>
+        <v>-132</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -824,7 +824,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -836,43 +836,43 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.218</v>
+        <v>0.2024</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="P2">
-        <v>4.5</v>
+        <v>4.21</v>
       </c>
       <c r="Q2">
-        <v>0.2091</v>
+        <v>0.26</v>
       </c>
       <c r="R2">
-        <v>0.355</v>
+        <v>0.333</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2567</v>
+        <v>0.161</v>
       </c>
       <c r="U2">
-        <v>0.2504</v>
+        <v>0.1765</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2374</v>
+        <v>0.1839</v>
       </c>
       <c r="X2">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y2">
-        <v>1.0287</v>
+        <v>0.88</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -881,22 +881,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>5.96</v>
+        <v>3.11</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2149</v>
+        <v>0.2216</v>
       </c>
       <c r="AG2">
-        <v>1.1661</v>
+        <v>0.7203</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>5.96</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -907,13 +907,13 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D3">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E3">
-        <v>-132</v>
+        <v>-148</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
@@ -925,7 +925,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -937,43 +937,43 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>0.2028</v>
+        <v>0.2175</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="P3">
-        <v>4.2</v>
+        <v>4.48</v>
       </c>
       <c r="Q3">
-        <v>0.2727</v>
+        <v>0.1935</v>
       </c>
       <c r="R3">
-        <v>0.377</v>
+        <v>0.317</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.161</v>
+        <v>0.2567</v>
       </c>
       <c r="U3">
-        <v>0.1765</v>
+        <v>0.2504</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.1839</v>
+        <v>0.2374</v>
       </c>
       <c r="X3">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y3">
-        <v>0.88</v>
+        <v>1.0287</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -982,22 +982,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.37</v>
+        <v>5.56</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2291</v>
+        <v>0.2099</v>
       </c>
       <c r="AG3">
-        <v>0.7313</v>
+        <v>1.1485</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.37</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1011,22 +1011,22 @@
         <v>4.5</v>
       </c>
       <c r="D4">
-        <v>-104</v>
+        <v>-150</v>
       </c>
       <c r="E4">
-        <v>-110</v>
+        <v>120</v>
       </c>
       <c r="F4" t="s">
         <v>48</v>
       </c>
       <c r="G4">
-        <v>824880</v>
+        <v>823344</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1038,43 +1038,43 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.2365</v>
+        <v>0.2132</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="P4">
-        <v>4.07</v>
+        <v>4.53</v>
       </c>
       <c r="Q4">
-        <v>0.2396</v>
+        <v>0.2051</v>
       </c>
       <c r="R4">
-        <v>0.324</v>
+        <v>0.369</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2336</v>
+        <v>0.3018</v>
       </c>
       <c r="U4">
-        <v>0.2296</v>
+        <v>0.3006</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>0.218</v>
+        <v>0.2571</v>
       </c>
       <c r="X4">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y4">
-        <v>1.0284</v>
+        <v>1.1015</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1083,22 +1083,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>5.68</v>
+        <v>7.09</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF4">
-        <v>0.2375</v>
+        <v>0.2102</v>
       </c>
       <c r="AG4">
-        <v>1.0608</v>
+        <v>1.3499</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="AM4">
-        <v>5.68</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1106,76 +1106,67 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5">
-        <v>3.5</v>
-      </c>
-      <c r="D5">
-        <v>-130</v>
-      </c>
-      <c r="E5">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
         <v>48</v>
       </c>
       <c r="G5">
-        <v>824880</v>
+        <v>823344</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I5">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>0.1942</v>
+        <v>0.2519</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O5">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="P5">
-        <v>4.22</v>
+        <v>4.11</v>
       </c>
       <c r="Q5">
-        <v>0.1818</v>
+        <v>0.3056</v>
       </c>
       <c r="R5">
-        <v>0.377</v>
+        <v>0.153</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.1833</v>
+        <v>0.2086</v>
       </c>
       <c r="U5">
-        <v>0.179</v>
+        <v>0.1946</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.1991</v>
+        <v>0.2177</v>
       </c>
       <c r="X5">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y5">
-        <v>0.88</v>
+        <v>0.9171</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1184,22 +1175,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>3.36</v>
+        <v>2.06</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.1896</v>
+        <v>0.26</v>
       </c>
       <c r="AG5">
-        <v>0.8326</v>
+        <v>0.9333</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>3.36</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1207,28 +1198,28 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>4.5</v>
       </c>
       <c r="D6">
-        <v>-150</v>
+        <v>-104</v>
       </c>
       <c r="E6">
-        <v>120</v>
+        <v>-110</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G6">
-        <v>823344</v>
+        <v>824880</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1240,43 +1231,43 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>0.2132</v>
+        <v>0.2365</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="P6">
-        <v>4.53</v>
+        <v>4.07</v>
       </c>
       <c r="Q6">
-        <v>0.2051</v>
+        <v>0.2396</v>
       </c>
       <c r="R6">
-        <v>0.369</v>
+        <v>0.324</v>
       </c>
       <c r="S6" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2169</v>
+        <v>0.2336</v>
       </c>
       <c r="U6">
-        <v>0.2405</v>
+        <v>0.2296</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>0.2571</v>
+        <v>0.218</v>
       </c>
       <c r="X6">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y6">
-        <v>1.0248</v>
+        <v>1.0284</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1285,22 +1276,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.81</v>
+        <v>5.6</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.2102</v>
+        <v>0.2375</v>
       </c>
       <c r="AG6">
-        <v>0.985</v>
+        <v>1.0448</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>4.81</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1308,28 +1299,28 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7">
+        <v>3.5</v>
+      </c>
+      <c r="D7">
+        <v>-130</v>
+      </c>
+      <c r="E7">
+        <v>118</v>
+      </c>
+      <c r="F7" t="s">
         <v>53</v>
       </c>
-      <c r="C7">
-        <v>8.5</v>
-      </c>
-      <c r="D7">
-        <v>100</v>
-      </c>
-      <c r="E7">
-        <v>-110</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
       <c r="G7">
-        <v>822774</v>
+        <v>824880</v>
       </c>
       <c r="H7" t="s">
         <v>42</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1341,43 +1332,43 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>0.3611</v>
+        <v>0.1942</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="P7">
-        <v>4.03</v>
+        <v>4.22</v>
       </c>
       <c r="Q7">
-        <v>0.3359</v>
+        <v>0.1818</v>
       </c>
       <c r="R7">
-        <v>0.39</v>
+        <v>0.377</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2423</v>
+        <v>0.1833</v>
       </c>
       <c r="U7">
-        <v>0.2445</v>
+        <v>0.179</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.244</v>
+        <v>0.1991</v>
       </c>
       <c r="X7">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y7">
-        <v>1.0285</v>
+        <v>0.88</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1386,22 +1377,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>9.56</v>
+        <v>3.31</v>
       </c>
       <c r="AE7" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.3513</v>
+        <v>0.1896</v>
       </c>
       <c r="AG7">
-        <v>1.1006</v>
+        <v>0.82</v>
       </c>
       <c r="AH7">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>8.74</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1409,7 +1400,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8">
         <v>4.5</v>
@@ -1421,7 +1412,7 @@
         <v>125</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>822774</v>
@@ -1475,7 +1466,7 @@
         <v>0.2108</v>
       </c>
       <c r="X8">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y8">
         <v>0.9762</v>
@@ -1487,7 +1478,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.71</v>
+        <v>4.64</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
@@ -1496,13 +1487,13 @@
         <v>0.2462</v>
       </c>
       <c r="AG8">
-        <v>0.8589</v>
+        <v>0.846</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>4.71</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1513,28 +1504,28 @@
         <v>57</v>
       </c>
       <c r="C9">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="D9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E9">
-        <v>-127</v>
+        <v>-110</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G9">
-        <v>824236</v>
+        <v>822774</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="I9">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
@@ -1543,43 +1534,43 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>0.268</v>
+        <v>0.3611</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O9">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="P9">
-        <v>4.29</v>
+        <v>4.03</v>
       </c>
       <c r="Q9">
-        <v>0.2667</v>
+        <v>0.3359</v>
       </c>
       <c r="R9">
-        <v>0.231</v>
+        <v>0.39</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2411</v>
+        <v>0.2423</v>
       </c>
       <c r="U9">
-        <v>0.2457</v>
+        <v>0.2445</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.2366</v>
+        <v>0.244</v>
       </c>
       <c r="X9">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y9">
-        <v>1.0113</v>
+        <v>1.0285</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1588,22 +1579,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.81</v>
+        <v>9.42</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF9">
-        <v>0.2677</v>
+        <v>0.3513</v>
       </c>
       <c r="AG9">
-        <v>1.095</v>
+        <v>1.084</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="AM9">
-        <v>3.81</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1611,28 +1602,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C10">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D10">
-        <v>-120</v>
+        <v>136</v>
       </c>
       <c r="E10">
-        <v>101</v>
+        <v>-155</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10">
-        <v>824236</v>
+        <v>823590</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1644,43 +1635,43 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>0.2764</v>
+        <v>0.2308</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="P10">
-        <v>4.05</v>
+        <v>4.38</v>
       </c>
       <c r="Q10">
-        <v>0.3217</v>
+        <v>0.2283</v>
       </c>
       <c r="R10">
-        <v>0.365</v>
+        <v>0.315</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.1936</v>
+        <v>0.2439</v>
       </c>
       <c r="U10">
-        <v>0.1946</v>
+        <v>0.2404</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2259</v>
+        <v>0.2247</v>
       </c>
       <c r="X10">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y10">
-        <v>0.88</v>
+        <v>0.9461</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1689,22 +1680,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>5.09</v>
+        <v>4.85</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.2929</v>
+        <v>0.23</v>
       </c>
       <c r="AG10">
-        <v>0.8795</v>
+        <v>1.0911</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>5.09</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1712,34 +1703,76 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D11">
-        <v>-111</v>
+        <v>-115</v>
       </c>
       <c r="E11">
-        <v>-105</v>
+        <v>115</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" t="s">
-        <v>44</v>
+        <v>59</v>
+      </c>
+      <c r="G11">
+        <v>823590</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I11">
+        <v>4.6</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
       </c>
       <c r="L11">
         <v>6</v>
       </c>
+      <c r="M11">
+        <v>0.2882</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11">
+        <v>107</v>
+      </c>
+      <c r="P11">
+        <v>4.34</v>
+      </c>
+      <c r="Q11">
+        <v>0.3084</v>
+      </c>
+      <c r="R11">
+        <v>0.349</v>
+      </c>
       <c r="S11" t="s">
-        <v>44</v>
-      </c>
-      <c r="V11" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T11">
+        <v>0.2111</v>
+      </c>
+      <c r="U11">
+        <v>0.2194</v>
+      </c>
+      <c r="V11">
+        <v>9</v>
+      </c>
+      <c r="W11">
+        <v>0.2066</v>
+      </c>
+      <c r="X11">
+        <v>0.2236</v>
+      </c>
+      <c r="Y11">
+        <v>0.9898</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1747,8 +1780,23 @@
       <c r="AC11" t="s">
         <v>44</v>
       </c>
+      <c r="AD11">
+        <v>5.52</v>
+      </c>
       <c r="AE11" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF11">
+        <v>0.2953</v>
+      </c>
+      <c r="AG11">
+        <v>0.9444</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>5.52</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1756,28 +1804,28 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C12">
         <v>4.5</v>
       </c>
       <c r="D12">
-        <v>-120</v>
+        <v>132</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>-161</v>
       </c>
       <c r="F12" t="s">
         <v>62</v>
       </c>
       <c r="G12">
-        <v>824477</v>
+        <v>824397</v>
       </c>
       <c r="H12" t="s">
         <v>42</v>
       </c>
       <c r="I12">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1789,43 +1837,43 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.1852</v>
+        <v>0.2377</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="P12">
-        <v>4.46</v>
+        <v>4.03</v>
       </c>
       <c r="Q12">
-        <v>0.2277</v>
+        <v>0.1869</v>
       </c>
       <c r="R12">
-        <v>0.336</v>
+        <v>0.349</v>
       </c>
       <c r="S12" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.2391</v>
+        <v>0.1882</v>
       </c>
       <c r="U12">
-        <v>0.2316</v>
+        <v>0.1862</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2334</v>
+        <v>0.2144</v>
       </c>
       <c r="X12">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y12">
-        <v>0.9913</v>
+        <v>0.88</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1834,22 +1882,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.91</v>
+        <v>3.5</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.1995</v>
+        <v>0.22</v>
       </c>
       <c r="AG12">
-        <v>1.0859</v>
+        <v>0.8418</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>4.91</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1857,19 +1905,19 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13">
         <v>4.5</v>
       </c>
       <c r="D13">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="E13">
-        <v>-161</v>
+        <v>-113</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>824397</v>
@@ -1878,7 +1926,7 @@
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1890,43 +1938,43 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.2377</v>
+        <v>0.1945</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="P13">
-        <v>4.03</v>
+        <v>4.06</v>
       </c>
       <c r="Q13">
-        <v>0.1869</v>
+        <v>0.2093</v>
       </c>
       <c r="R13">
-        <v>0.349</v>
+        <v>0.392</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.1882</v>
+        <v>0.1833</v>
       </c>
       <c r="U13">
-        <v>0.1862</v>
+        <v>0.1798</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2144</v>
+        <v>0.2183</v>
       </c>
       <c r="X13">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y13">
-        <v>0.88</v>
+        <v>1.0127</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1935,22 +1983,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.22</v>
+        <v>0.2003</v>
       </c>
       <c r="AG13">
-        <v>0.8547</v>
+        <v>0.8198</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1958,28 +2006,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D14">
-        <v>117</v>
+        <v>-120</v>
       </c>
       <c r="E14">
-        <v>-113</v>
+        <v>101</v>
       </c>
       <c r="F14" t="s">
         <v>65</v>
       </c>
       <c r="G14">
-        <v>824397</v>
+        <v>824236</v>
       </c>
       <c r="H14" t="s">
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1991,43 +2039,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.1945</v>
+        <v>0.2764</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="P14">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="Q14">
-        <v>0.2093</v>
+        <v>0.3217</v>
       </c>
       <c r="R14">
-        <v>0.392</v>
+        <v>0.365</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
       </c>
       <c r="T14">
-        <v>0.1833</v>
+        <v>0.1936</v>
       </c>
       <c r="U14">
-        <v>0.1798</v>
+        <v>0.1946</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>0.2183</v>
+        <v>0.2259</v>
       </c>
       <c r="X14">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y14">
-        <v>1.0127</v>
+        <v>0.88</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2036,22 +2084,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.96</v>
+        <v>5.01</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.2003</v>
+        <v>0.2929</v>
       </c>
       <c r="AG14">
-        <v>0.8323</v>
+        <v>0.8662</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>3.96</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2059,31 +2107,31 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15">
         <v>4.5</v>
       </c>
       <c r="D15">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="E15">
-        <v>-155</v>
+        <v>-127</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G15">
-        <v>823590</v>
+        <v>824236</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I15">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2092,43 +2140,43 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2308</v>
+        <v>0.268</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O15">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="P15">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="Q15">
-        <v>0.2283</v>
+        <v>0.2667</v>
       </c>
       <c r="R15">
-        <v>0.315</v>
+        <v>0.231</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2439</v>
+        <v>0.2411</v>
       </c>
       <c r="U15">
-        <v>0.2404</v>
+        <v>0.2457</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2247</v>
+        <v>0.2366</v>
       </c>
       <c r="X15">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y15">
-        <v>0.9461</v>
+        <v>1.0113</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2137,22 +2185,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>4.92</v>
+        <v>3.76</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.23</v>
+        <v>0.2677</v>
       </c>
       <c r="AG15">
-        <v>1.1078</v>
+        <v>1.0785</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>4.92</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2160,28 +2208,19 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16">
-        <v>5.5</v>
-      </c>
-      <c r="D16">
-        <v>-115</v>
-      </c>
-      <c r="E16">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="F16" t="s">
         <v>68</v>
       </c>
       <c r="G16">
-        <v>823590</v>
+        <v>824477</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
       <c r="I16">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2190,46 +2229,46 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>0.2882</v>
+        <v>0.2718</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="P16">
-        <v>4.34</v>
+        <v>4.04</v>
       </c>
       <c r="Q16">
-        <v>0.3084</v>
+        <v>0.2705</v>
       </c>
       <c r="R16">
-        <v>0.349</v>
+        <v>0.379</v>
       </c>
       <c r="S16" t="s">
         <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2111</v>
+        <v>0.2811</v>
       </c>
       <c r="U16">
-        <v>0.2194</v>
+        <v>0.269</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2066</v>
+        <v>0.2543</v>
       </c>
       <c r="X16">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y16">
-        <v>0.9898</v>
+        <v>1.0914</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2238,22 +2277,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>5.6</v>
+        <v>8.35</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF16">
-        <v>0.2953</v>
+        <v>0.2713</v>
       </c>
       <c r="AG16">
-        <v>0.9589</v>
+        <v>1.2574</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="AM16">
-        <v>5.6</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2261,28 +2300,28 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D17">
-        <v>-134</v>
+        <v>-120</v>
       </c>
       <c r="E17">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G17">
-        <v>823670</v>
+        <v>824477</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2294,43 +2333,43 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>0.1917</v>
+        <v>0.1852</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P17">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="Q17">
-        <v>0.23</v>
+        <v>0.2277</v>
       </c>
       <c r="R17">
-        <v>0.333</v>
+        <v>0.336</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2249</v>
+        <v>0.2398</v>
       </c>
       <c r="U17">
-        <v>0.212</v>
+        <v>0.2075</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2114</v>
+        <v>0.2334</v>
       </c>
       <c r="X17">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y17">
-        <v>1</v>
+        <v>0.8813</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2339,22 +2378,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.39</v>
+        <v>4.31</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.2044</v>
+        <v>0.1995</v>
       </c>
       <c r="AG17">
-        <v>1.0215</v>
+        <v>1.0726</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.39</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2362,16 +2401,16 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C18">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D18">
-        <v>120</v>
+        <v>-134</v>
       </c>
       <c r="E18">
-        <v>-132</v>
+        <v>110</v>
       </c>
       <c r="F18" t="s">
         <v>71</v>
@@ -2383,7 +2422,7 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2395,43 +2434,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.2423</v>
+        <v>0.1917</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>4.04</v>
+        <v>4.48</v>
       </c>
       <c r="Q18">
-        <v>0.213</v>
+        <v>0.23</v>
       </c>
       <c r="R18">
-        <v>0.351</v>
+        <v>0.333</v>
       </c>
       <c r="S18" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="T18">
-        <v>0.1823</v>
+        <v>0.2249</v>
       </c>
       <c r="U18">
-        <v>0.1844</v>
+        <v>0.212</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2249</v>
+        <v>0.2114</v>
       </c>
       <c r="X18">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y18">
-        <v>0.9614</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2440,22 +2479,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>3.98</v>
+        <v>4.32</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.232</v>
+        <v>0.2044</v>
       </c>
       <c r="AG18">
-        <v>0.828</v>
+        <v>1.0061</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>3.98</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2463,28 +2502,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D19">
-        <v>-128</v>
+        <v>120</v>
       </c>
       <c r="E19">
-        <v>110</v>
+        <v>-132</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G19">
-        <v>824642</v>
+        <v>823670</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2496,43 +2535,43 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.2199</v>
+        <v>0.2423</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="P19">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="Q19">
-        <v>0.2105</v>
+        <v>0.213</v>
       </c>
       <c r="R19">
-        <v>0.363</v>
+        <v>0.351</v>
       </c>
       <c r="S19" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="T19">
-        <v>0.2297</v>
+        <v>0.1834</v>
       </c>
       <c r="U19">
-        <v>0.227</v>
+        <v>0.1839</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2172</v>
+        <v>0.2249</v>
       </c>
       <c r="X19">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y19">
-        <v>0.9679</v>
+        <v>0.9041</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2541,22 +2580,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.79</v>
+        <v>3.71</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2165</v>
+        <v>0.232</v>
       </c>
       <c r="AG19">
-        <v>1.0435</v>
+        <v>0.8206</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>4.79</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2564,16 +2603,16 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D20">
-        <v>139</v>
+        <v>-128</v>
       </c>
       <c r="E20">
-        <v>-158</v>
+        <v>110</v>
       </c>
       <c r="F20" t="s">
         <v>74</v>
@@ -2597,43 +2636,43 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.2104</v>
+        <v>0.2199</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="P20">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="Q20">
-        <v>0.2041</v>
+        <v>0.2105</v>
       </c>
       <c r="R20">
-        <v>0.329</v>
+        <v>0.363</v>
       </c>
       <c r="S20" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T20">
-        <v>0.2</v>
+        <v>0.2297</v>
       </c>
       <c r="U20">
-        <v>0.1889</v>
+        <v>0.227</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2125</v>
+        <v>0.2172</v>
       </c>
       <c r="X20">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y20">
-        <v>0.9582</v>
+        <v>0.9679</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2642,22 +2681,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4</v>
+        <v>4.72</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.2083</v>
+        <v>0.2165</v>
       </c>
       <c r="AG20">
-        <v>0.9083</v>
+        <v>1.0277</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>4</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2671,22 +2710,22 @@
         <v>4.5</v>
       </c>
       <c r="D21">
-        <v>-115</v>
+        <v>139</v>
       </c>
       <c r="E21">
-        <v>-105</v>
+        <v>-158</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G21">
-        <v>823182</v>
+        <v>824642</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
       </c>
       <c r="I21">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2698,43 +2737,43 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.2088</v>
+        <v>0.2104</v>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O21">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="P21">
-        <v>4.01</v>
+        <v>4.27</v>
       </c>
       <c r="Q21">
-        <v>0.2045</v>
+        <v>0.2041</v>
       </c>
       <c r="R21">
-        <v>0.18</v>
+        <v>0.329</v>
       </c>
       <c r="S21" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T21">
-        <v>0.2294</v>
+        <v>0.2</v>
       </c>
       <c r="U21">
-        <v>0.2268</v>
+        <v>0.1889</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>0.2177</v>
+        <v>0.2125</v>
       </c>
       <c r="X21">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y21">
-        <v>1.0344</v>
+        <v>0.9582</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2743,22 +2782,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>4.8</v>
+        <v>3.94</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.208</v>
+        <v>0.2083</v>
       </c>
       <c r="AG21">
-        <v>1.0418</v>
+        <v>0.8946</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>4.8</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2766,7 +2805,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22">
         <v>3.5</v>
@@ -2778,7 +2817,7 @@
         <v>129</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G22">
         <v>823182</v>
@@ -2817,25 +2856,25 @@
         <v>0.351</v>
       </c>
       <c r="S22" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="T22">
-        <v>0.2138</v>
+        <v>0.2283</v>
       </c>
       <c r="U22">
-        <v>0.2142</v>
+        <v>0.2105</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>0.2015</v>
       </c>
       <c r="X22">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y22">
-        <v>1.0152</v>
+        <v>1.0015</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2844,7 +2883,7 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>4.61</v>
+        <v>4.78</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
@@ -2853,13 +2892,13 @@
         <v>0.2154</v>
       </c>
       <c r="AG22">
-        <v>0.9708</v>
+        <v>1.0212</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>4.61</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2873,28 +2912,70 @@
         <v>4.5</v>
       </c>
       <c r="D23">
-        <v>132</v>
+        <v>-115</v>
       </c>
       <c r="E23">
-        <v>-148</v>
+        <v>-105</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
-      </c>
-      <c r="G23" t="s">
-        <v>44</v>
+        <v>78</v>
+      </c>
+      <c r="G23">
+        <v>823182</v>
       </c>
       <c r="H23" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I23">
+        <v>5.3</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
       </c>
       <c r="L23">
         <v>6</v>
       </c>
+      <c r="M23">
+        <v>0.2088</v>
+      </c>
+      <c r="N23">
+        <v>2</v>
+      </c>
+      <c r="O23">
+        <v>44</v>
+      </c>
+      <c r="P23">
+        <v>4.01</v>
+      </c>
+      <c r="Q23">
+        <v>0.2045</v>
+      </c>
+      <c r="R23">
+        <v>0.18</v>
+      </c>
       <c r="S23" t="s">
-        <v>44</v>
-      </c>
-      <c r="V23" t="s">
-        <v>44</v>
+        <v>75</v>
+      </c>
+      <c r="T23">
+        <v>0.2294</v>
+      </c>
+      <c r="U23">
+        <v>0.2268</v>
+      </c>
+      <c r="V23">
+        <v>9</v>
+      </c>
+      <c r="W23">
+        <v>0.2177</v>
+      </c>
+      <c r="X23">
+        <v>0.2236</v>
+      </c>
+      <c r="Y23">
+        <v>1.0344</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2902,8 +2983,23 @@
       <c r="AC23" t="s">
         <v>44</v>
       </c>
+      <c r="AD23">
+        <v>4.73</v>
+      </c>
       <c r="AE23" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF23">
+        <v>0.208</v>
+      </c>
+      <c r="AG23">
+        <v>1.0261</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>4.73</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2911,7 +3007,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24">
         <v>4.5</v>
@@ -2923,7 +3019,7 @@
         <v>112</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G24">
         <v>824965</v>
@@ -2962,7 +3058,7 @@
         <v>0.355</v>
       </c>
       <c r="S24" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T24">
         <v>0.2174</v>
@@ -2977,7 +3073,7 @@
         <v>0.2467</v>
       </c>
       <c r="X24">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y24">
         <v>1.0364</v>
@@ -2989,7 +3085,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>4.93</v>
+        <v>4.86</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
@@ -2998,13 +3094,13 @@
         <v>0.2319</v>
       </c>
       <c r="AG24">
-        <v>0.9875</v>
+        <v>0.9726</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>4.93</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3063,7 +3159,7 @@
         <v>0.396</v>
       </c>
       <c r="S25" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T25">
         <v>0.2689</v>
@@ -3078,7 +3174,7 @@
         <v>0.2557</v>
       </c>
       <c r="X25">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y25">
         <v>1.0285</v>
@@ -3090,7 +3186,7 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>6.37</v>
+        <v>6.27</v>
       </c>
       <c r="AE25" t="s">
         <v>84</v>
@@ -3099,13 +3195,13 @@
         <v>0.214</v>
       </c>
       <c r="AG25">
-        <v>1.2212</v>
+        <v>1.2027</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>6.37</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3164,7 +3260,7 @@
         <v>0.333</v>
       </c>
       <c r="S26" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T26">
         <v>0.2065</v>
@@ -3179,7 +3275,7 @@
         <v>0.2102</v>
       </c>
       <c r="X26">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y26">
         <v>0.989</v>
@@ -3191,7 +3287,7 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
@@ -3200,13 +3296,13 @@
         <v>0.1751</v>
       </c>
       <c r="AG26">
-        <v>0.9377</v>
+        <v>0.9235</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3217,13 +3313,13 @@
         <v>86</v>
       </c>
       <c r="C27">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D27">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E27">
-        <v>-136</v>
+        <v>-120</v>
       </c>
       <c r="F27" t="s">
         <v>87</v>
@@ -3235,7 +3331,7 @@
         <v>42</v>
       </c>
       <c r="I27">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3247,43 +3343,43 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.3055</v>
+        <v>0.3194</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="P27">
-        <v>3.89</v>
+        <v>3.83</v>
       </c>
       <c r="Q27">
-        <v>0.3197</v>
+        <v>0.3333</v>
       </c>
       <c r="R27">
-        <v>0.379</v>
+        <v>0.344</v>
       </c>
       <c r="S27" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T27">
-        <v>0.2086</v>
+        <v>0.2849</v>
       </c>
       <c r="U27">
-        <v>0.2372</v>
+        <v>0.2218</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2198</v>
+        <v>0.2073</v>
       </c>
       <c r="X27">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y27">
-        <v>1.0017</v>
+        <v>0.993</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3292,22 +3388,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>6.87</v>
+        <v>8.06</v>
       </c>
       <c r="AE27" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="AF27">
-        <v>0.3109</v>
+        <v>0.3242</v>
       </c>
       <c r="AG27">
-        <v>0.9472</v>
+        <v>1.2743</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="AM27">
-        <v>6.87</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3318,13 +3414,13 @@
         <v>88</v>
       </c>
       <c r="C28">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="D28">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E28">
-        <v>-120</v>
+        <v>-136</v>
       </c>
       <c r="F28" t="s">
         <v>87</v>
@@ -3336,7 +3432,7 @@
         <v>42</v>
       </c>
       <c r="I28">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3348,43 +3444,43 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>0.3194</v>
+        <v>0.3055</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="P28">
-        <v>3.83</v>
+        <v>3.89</v>
       </c>
       <c r="Q28">
-        <v>0.3333</v>
+        <v>0.3197</v>
       </c>
       <c r="R28">
-        <v>0.344</v>
+        <v>0.379</v>
       </c>
       <c r="S28" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T28">
-        <v>0.2849</v>
+        <v>0.2086</v>
       </c>
       <c r="U28">
-        <v>0.2218</v>
+        <v>0.2372</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>0.2073</v>
+        <v>0.2198</v>
       </c>
       <c r="X28">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y28">
-        <v>0.993</v>
+        <v>1.0017</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3393,22 +3489,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>8.18</v>
+        <v>6.76</v>
       </c>
       <c r="AE28" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="AF28">
-        <v>0.3242</v>
+        <v>0.3109</v>
       </c>
       <c r="AG28">
-        <v>1.2938</v>
+        <v>0.9329</v>
       </c>
       <c r="AH28">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>7.36</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3422,10 +3518,10 @@
         <v>5.5</v>
       </c>
       <c r="D29">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="E29">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="F29" t="s">
         <v>90</v>
@@ -3437,7 +3533,7 @@
         <v>42</v>
       </c>
       <c r="I29">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3449,43 +3545,43 @@
         <v>6</v>
       </c>
       <c r="M29">
-        <v>0.2491</v>
+        <v>0.244</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P29">
-        <v>4.23</v>
+        <v>4.09</v>
       </c>
       <c r="Q29">
-        <v>0.2414</v>
+        <v>0.2564</v>
       </c>
       <c r="R29">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="S29" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T29">
-        <v>0.2027</v>
+        <v>0.208</v>
       </c>
       <c r="U29">
-        <v>0.1929</v>
+        <v>0.1979</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>0.2251</v>
+        <v>0.2159</v>
       </c>
       <c r="X29">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y29">
-        <v>0.9948</v>
+        <v>0.9971</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3494,22 +3590,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>5.05</v>
+        <v>5.42</v>
       </c>
       <c r="AE29" t="s">
         <v>45</v>
       </c>
       <c r="AF29">
-        <v>0.2462</v>
+        <v>0.2486</v>
       </c>
       <c r="AG29">
-        <v>0.9205</v>
+        <v>0.9304</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>5.05</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3523,10 +3619,10 @@
         <v>5.5</v>
       </c>
       <c r="D30">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="E30">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="F30" t="s">
         <v>90</v>
@@ -3538,7 +3634,7 @@
         <v>42</v>
       </c>
       <c r="I30">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3550,43 +3646,43 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>0.244</v>
+        <v>0.2491</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P30">
-        <v>4.09</v>
+        <v>4.23</v>
       </c>
       <c r="Q30">
-        <v>0.2564</v>
+        <v>0.2414</v>
       </c>
       <c r="R30">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="S30" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="T30">
-        <v>0.208</v>
+        <v>0.2027</v>
       </c>
       <c r="U30">
-        <v>0.1979</v>
+        <v>0.1929</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W30">
-        <v>0.2159</v>
+        <v>0.2251</v>
       </c>
       <c r="X30">
-        <v>0.2202</v>
+        <v>0.2236</v>
       </c>
       <c r="Y30">
-        <v>0.9971</v>
+        <v>0.9948</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3595,22 +3691,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>5.51</v>
+        <v>4.98</v>
       </c>
       <c r="AE30" t="s">
         <v>45</v>
       </c>
       <c r="AF30">
-        <v>0.2486</v>
+        <v>0.2462</v>
       </c>
       <c r="AG30">
-        <v>0.9447</v>
+        <v>0.9066</v>
       </c>
       <c r="AH30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>5.51</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3620,65 +3716,32 @@
       <c r="B31" t="s">
         <v>92</v>
       </c>
+      <c r="C31">
+        <v>6.5</v>
+      </c>
+      <c r="D31">
+        <v>-111</v>
+      </c>
+      <c r="E31">
+        <v>-105</v>
+      </c>
       <c r="F31" t="s">
-        <v>51</v>
-      </c>
-      <c r="G31">
-        <v>823344</v>
+        <v>68</v>
+      </c>
+      <c r="G31" t="s">
+        <v>44</v>
       </c>
       <c r="H31" t="s">
-        <v>59</v>
-      </c>
-      <c r="I31">
-        <v>2.3</v>
-      </c>
-      <c r="J31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0.2519</v>
-      </c>
-      <c r="N31">
-        <v>4</v>
-      </c>
-      <c r="O31">
-        <v>36</v>
-      </c>
-      <c r="P31">
-        <v>4.11</v>
-      </c>
-      <c r="Q31">
-        <v>0.3056</v>
-      </c>
-      <c r="R31">
-        <v>0.153</v>
+        <v>6</v>
       </c>
       <c r="S31" t="s">
-        <v>43</v>
-      </c>
-      <c r="T31">
-        <v>0.2086</v>
-      </c>
-      <c r="U31">
-        <v>0.1946</v>
-      </c>
-      <c r="V31">
-        <v>9</v>
-      </c>
-      <c r="W31">
-        <v>0.2177</v>
-      </c>
-      <c r="X31">
-        <v>0.2202</v>
-      </c>
-      <c r="Y31">
-        <v>0.9171</v>
+        <v>44</v>
+      </c>
+      <c r="V31" t="s">
+        <v>44</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3686,23 +3749,8 @@
       <c r="AC31" t="s">
         <v>44</v>
       </c>
-      <c r="AD31">
-        <v>2.09</v>
-      </c>
       <c r="AE31" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF31">
-        <v>0.26</v>
-      </c>
-      <c r="AG31">
-        <v>0.9476</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>2.09</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3712,65 +3760,32 @@
       <c r="B32" t="s">
         <v>93</v>
       </c>
+      <c r="C32">
+        <v>4.5</v>
+      </c>
+      <c r="D32">
+        <v>132</v>
+      </c>
+      <c r="E32">
+        <v>-148</v>
+      </c>
       <c r="F32" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32">
-        <v>824477</v>
+        <v>81</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
-      </c>
-      <c r="I32">
-        <v>5.6</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0.2718</v>
-      </c>
-      <c r="N32">
-        <v>5</v>
-      </c>
-      <c r="O32">
-        <v>122</v>
-      </c>
-      <c r="P32">
-        <v>4.04</v>
-      </c>
-      <c r="Q32">
-        <v>0.2705</v>
-      </c>
-      <c r="R32">
-        <v>0.379</v>
+        <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>43</v>
-      </c>
-      <c r="T32">
-        <v>0.2811</v>
-      </c>
-      <c r="U32">
-        <v>0.269</v>
-      </c>
-      <c r="V32">
-        <v>9</v>
-      </c>
-      <c r="W32">
-        <v>0.2543</v>
-      </c>
-      <c r="X32">
-        <v>0.2202</v>
-      </c>
-      <c r="Y32">
-        <v>1.0914</v>
+        <v>44</v>
+      </c>
+      <c r="V32" t="s">
+        <v>44</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3778,23 +3793,8 @@
       <c r="AC32" t="s">
         <v>44</v>
       </c>
-      <c r="AD32">
-        <v>8.48</v>
-      </c>
       <c r="AE32" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF32">
-        <v>0.2713</v>
-      </c>
-      <c r="AG32">
-        <v>1.2767</v>
-      </c>
-      <c r="AH32">
-        <v>-0.82</v>
-      </c>
-      <c r="AM32">
-        <v>7.66</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-16.xlsx
+++ b/data/k-props/2026-08-16.xlsx
@@ -160,33 +160,36 @@
     <t>Boston Red Sox @ Pittsburgh Pirates</t>
   </si>
   <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Lake Bachar</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Michael Soroka</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Bryce Elder</t>
+  </si>
+  <si>
+    <t>Ryan Weathers</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Dylan Cease</t>
+  </si>
+  <si>
     <t>&gt;=7</t>
   </si>
   <si>
-    <t>Lake Bachar</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Michael Soroka</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Bryce Elder</t>
-  </si>
-  <si>
-    <t>Ryan Weathers</t>
-  </si>
-  <si>
-    <t>New York Yankees @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>Dylan Cease</t>
-  </si>
-  <si>
     <t>Jake Irvin</t>
   </si>
   <si>
@@ -238,52 +241,49 @@
     <t>St. Louis Cardinals @ Chicago Cubs</t>
   </si>
   <si>
+    <t>Edward Cabrera</t>
+  </si>
+  <si>
+    <t>Gabriel Hughes</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Blade Tidwell</t>
+  </si>
+  <si>
+    <t>Jacob Lopez</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Athletics</t>
+  </si>
+  <si>
+    <t>Noah Cameron</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Ryan Johnson</t>
+  </si>
+  <si>
+    <t>Logan Henderson</t>
+  </si>
+  <si>
+    <t>Milwaukee Brewers @ Los Angeles Dodgers</t>
+  </si>
+  <si>
+    <t>Tarik Skubal</t>
+  </si>
+  <si>
+    <t>Bryan Woo</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Houston Astros</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Edward Cabrera</t>
-  </si>
-  <si>
-    <t>Gabriel Hughes</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Blade Tidwell</t>
-  </si>
-  <si>
-    <t>Jacob Lopez</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Athletics</t>
-  </si>
-  <si>
-    <t>Noah Cameron</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Ryan Johnson</t>
-  </si>
-  <si>
-    <t>Logan Henderson</t>
-  </si>
-  <si>
-    <t>Milwaukee Brewers @ Los Angeles Dodgers</t>
-  </si>
-  <si>
-    <t>Tarik Skubal</t>
-  </si>
-  <si>
-    <t>Bryan Woo</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Houston Astros</t>
   </si>
   <si>
     <t>Hunter Brown</t>
@@ -824,7 +824,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -836,22 +836,22 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.2024</v>
+        <v>0.2042</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="P2">
         <v>4.21</v>
       </c>
       <c r="Q2">
-        <v>0.26</v>
+        <v>0.2583</v>
       </c>
       <c r="R2">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
@@ -869,7 +869,7 @@
         <v>0.1839</v>
       </c>
       <c r="X2">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y2">
         <v>0.88</v>
@@ -881,22 +881,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2216</v>
+        <v>0.2245</v>
       </c>
       <c r="AG2">
-        <v>0.7203</v>
+        <v>0.7059</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>3.11</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -925,7 +925,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -937,22 +937,22 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>0.2175</v>
+        <v>0.2147</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="P3">
         <v>4.48</v>
       </c>
       <c r="Q3">
-        <v>0.1935</v>
+        <v>0.1776</v>
       </c>
       <c r="R3">
-        <v>0.317</v>
+        <v>0.349</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
@@ -970,7 +970,7 @@
         <v>0.2374</v>
       </c>
       <c r="X3">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y3">
         <v>1.0287</v>
@@ -982,22 +982,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>5.56</v>
+        <v>5.35</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2099</v>
+        <v>0.2017</v>
       </c>
       <c r="AG3">
-        <v>1.1485</v>
+        <v>1.1256</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>5.56</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1026,7 +1026,7 @@
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1038,22 +1038,22 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.2132</v>
+        <v>0.2129</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="P4">
-        <v>4.53</v>
+        <v>4.7</v>
       </c>
       <c r="Q4">
-        <v>0.2051</v>
+        <v>0.2035</v>
       </c>
       <c r="R4">
-        <v>0.369</v>
+        <v>0.361</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
@@ -1071,7 +1071,7 @@
         <v>0.2571</v>
       </c>
       <c r="X4">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y4">
         <v>1.1015</v>
@@ -1083,22 +1083,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>7.09</v>
+        <v>6.76</v>
       </c>
       <c r="AE4" t="s">
         <v>49</v>
       </c>
       <c r="AF4">
-        <v>0.2102</v>
+        <v>0.2095</v>
       </c>
       <c r="AG4">
-        <v>1.3499</v>
+        <v>1.323</v>
       </c>
       <c r="AH4">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>6.27</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1118,7 +1118,7 @@
         <v>51</v>
       </c>
       <c r="I5">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -1130,22 +1130,22 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0.2519</v>
+        <v>0.2562</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P5">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="Q5">
-        <v>0.3056</v>
+        <v>0.3191</v>
       </c>
       <c r="R5">
-        <v>0.153</v>
+        <v>0.19</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
@@ -1163,7 +1163,7 @@
         <v>0.2177</v>
       </c>
       <c r="X5">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y5">
         <v>0.9171</v>
@@ -1175,22 +1175,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.26</v>
+        <v>0.2682</v>
       </c>
       <c r="AG5">
-        <v>0.9333</v>
+        <v>0.9147</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1231,22 +1231,22 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>0.2365</v>
+        <v>0.2372</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="P6">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q6">
-        <v>0.2396</v>
+        <v>0.2472</v>
       </c>
       <c r="R6">
-        <v>0.324</v>
+        <v>0.308</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
@@ -1264,7 +1264,7 @@
         <v>0.218</v>
       </c>
       <c r="X6">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y6">
         <v>1.0284</v>
@@ -1276,22 +1276,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>5.6</v>
+        <v>5.52</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.2375</v>
+        <v>0.2403</v>
       </c>
       <c r="AG6">
-        <v>1.0448</v>
+        <v>1.024</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>5.6</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1332,22 +1332,22 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>0.1942</v>
+        <v>0.1927</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P7">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="Q7">
-        <v>0.1818</v>
+        <v>0.1765</v>
       </c>
       <c r="R7">
-        <v>0.377</v>
+        <v>0.373</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
@@ -1365,7 +1365,7 @@
         <v>0.1991</v>
       </c>
       <c r="X7">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y7">
         <v>0.88</v>
@@ -1377,22 +1377,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.1896</v>
+        <v>0.1867</v>
       </c>
       <c r="AG7">
-        <v>0.82</v>
+        <v>0.8037</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1433,22 +1433,22 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.259</v>
+        <v>0.2569</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="P8">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="Q8">
-        <v>0.2241</v>
+        <v>0.2243</v>
       </c>
       <c r="R8">
-        <v>0.367</v>
+        <v>0.349</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
@@ -1466,7 +1466,7 @@
         <v>0.2108</v>
       </c>
       <c r="X8">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y8">
         <v>0.9762</v>
@@ -1478,22 +1478,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.64</v>
+        <v>4.48</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.2462</v>
+        <v>0.2456</v>
       </c>
       <c r="AG8">
-        <v>0.846</v>
+        <v>0.8291</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>4.64</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1522,7 +1522,7 @@
         <v>42</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1534,22 +1534,22 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>0.3611</v>
+        <v>0.362</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="P9">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="Q9">
-        <v>0.3359</v>
+        <v>0.3583</v>
       </c>
       <c r="R9">
-        <v>0.39</v>
+        <v>0.375</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
@@ -1567,7 +1567,7 @@
         <v>0.244</v>
       </c>
       <c r="X9">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y9">
         <v>1.0285</v>
@@ -1579,22 +1579,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>9.42</v>
+        <v>9.37</v>
       </c>
       <c r="AE9" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="AF9">
-        <v>0.3513</v>
+        <v>0.3606</v>
       </c>
       <c r="AG9">
-        <v>1.084</v>
+        <v>1.0623</v>
       </c>
       <c r="AH9">
         <v>-0.82</v>
       </c>
       <c r="AM9">
-        <v>8.6</v>
+        <v>8.55</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1602,7 +1602,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>4.5</v>
@@ -1614,7 +1614,7 @@
         <v>-155</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G10">
         <v>823590</v>
@@ -1623,7 +1623,7 @@
         <v>42</v>
       </c>
       <c r="I10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1635,22 +1635,22 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>0.2308</v>
+        <v>0.2328</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P10">
-        <v>4.38</v>
+        <v>4.4</v>
       </c>
       <c r="Q10">
-        <v>0.2283</v>
+        <v>0.2111</v>
       </c>
       <c r="R10">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
@@ -1668,7 +1668,7 @@
         <v>0.2247</v>
       </c>
       <c r="X10">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y10">
         <v>0.9461</v>
@@ -1680,22 +1680,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>4.85</v>
+        <v>4.65</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.23</v>
+        <v>0.2261</v>
       </c>
       <c r="AG10">
-        <v>1.0911</v>
+        <v>1.0693</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>4.85</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1703,7 +1703,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>5.5</v>
@@ -1715,7 +1715,7 @@
         <v>115</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>823590</v>
@@ -1736,22 +1736,22 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2882</v>
+        <v>0.2893</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="P11">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="Q11">
-        <v>0.3084</v>
+        <v>0.301</v>
       </c>
       <c r="R11">
-        <v>0.349</v>
+        <v>0.34</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
@@ -1769,7 +1769,7 @@
         <v>0.2066</v>
       </c>
       <c r="X11">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y11">
         <v>0.9898</v>
@@ -1781,22 +1781,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.52</v>
+        <v>5.31</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.2953</v>
+        <v>0.2933</v>
       </c>
       <c r="AG11">
-        <v>0.9444</v>
+        <v>0.9255</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.52</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1804,7 +1804,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1816,7 +1816,7 @@
         <v>-161</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12">
         <v>824397</v>
@@ -1870,7 +1870,7 @@
         <v>0.2144</v>
       </c>
       <c r="X12">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y12">
         <v>0.88</v>
@@ -1882,7 +1882,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1891,13 +1891,13 @@
         <v>0.22</v>
       </c>
       <c r="AG12">
-        <v>0.8418</v>
+        <v>0.825</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1905,7 +1905,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C13">
         <v>4.5</v>
@@ -1917,7 +1917,7 @@
         <v>-113</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>824397</v>
@@ -1971,7 +1971,7 @@
         <v>0.2183</v>
       </c>
       <c r="X13">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y13">
         <v>1.0127</v>
@@ -1983,7 +1983,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
@@ -1992,13 +1992,13 @@
         <v>0.2003</v>
       </c>
       <c r="AG13">
-        <v>0.8198</v>
+        <v>0.8034</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2006,7 +2006,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -2018,7 +2018,7 @@
         <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14">
         <v>824236</v>
@@ -2027,7 +2027,7 @@
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2039,22 +2039,22 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.2764</v>
+        <v>0.2689</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="P14">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="Q14">
-        <v>0.3217</v>
+        <v>0.3028</v>
       </c>
       <c r="R14">
-        <v>0.365</v>
+        <v>0.353</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
@@ -2072,7 +2072,7 @@
         <v>0.2259</v>
       </c>
       <c r="X14">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y14">
         <v>0.88</v>
@@ -2084,22 +2084,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>5.01</v>
+        <v>4.64</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.2929</v>
+        <v>0.2808</v>
       </c>
       <c r="AG14">
-        <v>0.8662</v>
+        <v>0.849</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>5.01</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2107,7 +2107,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2119,7 +2119,7 @@
         <v>-127</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>824236</v>
@@ -2140,22 +2140,22 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.268</v>
+        <v>0.264</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="P15">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="Q15">
-        <v>0.2667</v>
+        <v>0.25</v>
       </c>
       <c r="R15">
-        <v>0.231</v>
+        <v>0.275</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
@@ -2173,7 +2173,7 @@
         <v>0.2366</v>
       </c>
       <c r="X15">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y15">
         <v>1.0113</v>
@@ -2185,22 +2185,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.76</v>
+        <v>3.57</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.2677</v>
+        <v>0.2601</v>
       </c>
       <c r="AG15">
-        <v>1.0785</v>
+        <v>1.057</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>3.76</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2208,10 +2208,10 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G16">
         <v>824477</v>
@@ -2220,7 +2220,7 @@
         <v>42</v>
       </c>
       <c r="I16">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2232,22 +2232,22 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0.2718</v>
+        <v>0.2712</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="P16">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="Q16">
-        <v>0.2705</v>
+        <v>0.2411</v>
       </c>
       <c r="R16">
-        <v>0.379</v>
+        <v>0.359</v>
       </c>
       <c r="S16" t="s">
         <v>43</v>
@@ -2265,7 +2265,7 @@
         <v>0.2543</v>
       </c>
       <c r="X16">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y16">
         <v>1.0914</v>
@@ -2277,22 +2277,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>8.35</v>
+        <v>7.69</v>
       </c>
       <c r="AE16" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="AF16">
-        <v>0.2713</v>
+        <v>0.2604</v>
       </c>
       <c r="AG16">
-        <v>1.2574</v>
+        <v>1.2323</v>
       </c>
       <c r="AH16">
         <v>-0.82</v>
       </c>
       <c r="AM16">
-        <v>7.53</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2300,7 +2300,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2312,7 +2312,7 @@
         <v>100</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G17">
         <v>824477</v>
@@ -2321,7 +2321,7 @@
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2333,22 +2333,22 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>0.1852</v>
+        <v>0.1821</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P17">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="Q17">
-        <v>0.2277</v>
+        <v>0.1863</v>
       </c>
       <c r="R17">
-        <v>0.336</v>
+        <v>0.338</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
@@ -2366,7 +2366,7 @@
         <v>0.2334</v>
       </c>
       <c r="X17">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y17">
         <v>0.8813</v>
@@ -2378,22 +2378,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.31</v>
+        <v>3.8</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.1995</v>
+        <v>0.1835</v>
       </c>
       <c r="AG17">
-        <v>1.0726</v>
+        <v>1.0512</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.31</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2401,7 +2401,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18">
         <v>3.5</v>
@@ -2413,7 +2413,7 @@
         <v>110</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G18">
         <v>823670</v>
@@ -2422,7 +2422,7 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2434,22 +2434,22 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.1917</v>
+        <v>0.1865</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="P18">
-        <v>4.48</v>
+        <v>4.49</v>
       </c>
       <c r="Q18">
-        <v>0.23</v>
+        <v>0.2235</v>
       </c>
       <c r="R18">
-        <v>0.333</v>
+        <v>0.298</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
@@ -2467,7 +2467,7 @@
         <v>0.2114</v>
       </c>
       <c r="X18">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y18">
         <v>1</v>
@@ -2479,22 +2479,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.32</v>
+        <v>3.96</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.2044</v>
+        <v>0.1975</v>
       </c>
       <c r="AG18">
-        <v>1.0061</v>
+        <v>0.986</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.32</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2502,7 +2502,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2514,7 +2514,7 @@
         <v>-132</v>
       </c>
       <c r="F19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G19">
         <v>823670</v>
@@ -2523,7 +2523,7 @@
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2535,22 +2535,22 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.2423</v>
+        <v>0.2438</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="P19">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="Q19">
-        <v>0.213</v>
+        <v>0.2041</v>
       </c>
       <c r="R19">
-        <v>0.351</v>
+        <v>0.329</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
@@ -2568,7 +2568,7 @@
         <v>0.2249</v>
       </c>
       <c r="X19">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y19">
         <v>0.9041</v>
@@ -2580,22 +2580,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>3.71</v>
+        <v>3.37</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.232</v>
+        <v>0.2307</v>
       </c>
       <c r="AG19">
-        <v>0.8206</v>
+        <v>0.8042</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>3.71</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2603,7 +2603,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20">
         <v>3.5</v>
@@ -2615,7 +2615,7 @@
         <v>110</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G20">
         <v>824642</v>
@@ -2654,13 +2654,13 @@
         <v>0.363</v>
       </c>
       <c r="S20" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2297</v>
+        <v>0.2431</v>
       </c>
       <c r="U20">
-        <v>0.227</v>
+        <v>0.2333</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2669,10 +2669,10 @@
         <v>0.2172</v>
       </c>
       <c r="X20">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y20">
-        <v>0.9679</v>
+        <v>0.9429</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2681,7 +2681,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.72</v>
+        <v>4.77</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
@@ -2690,13 +2690,13 @@
         <v>0.2165</v>
       </c>
       <c r="AG20">
-        <v>1.0277</v>
+        <v>1.0659</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>4.72</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2716,7 +2716,7 @@
         <v>-158</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G21">
         <v>824642</v>
@@ -2755,25 +2755,25 @@
         <v>0.329</v>
       </c>
       <c r="S21" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T21">
-        <v>0.2</v>
+        <v>0.176</v>
       </c>
       <c r="U21">
-        <v>0.1889</v>
+        <v>0.1952</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>0.2125</v>
       </c>
       <c r="X21">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y21">
-        <v>0.9582</v>
+        <v>0.915</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2782,7 +2782,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2791,13 +2791,13 @@
         <v>0.2083</v>
       </c>
       <c r="AG21">
-        <v>0.8946</v>
+        <v>0.7717</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2871,7 +2871,7 @@
         <v>0.2015</v>
       </c>
       <c r="X22">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y22">
         <v>1.0015</v>
@@ -2883,7 +2883,7 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>4.78</v>
+        <v>4.69</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
@@ -2892,13 +2892,13 @@
         <v>0.2154</v>
       </c>
       <c r="AG22">
-        <v>1.0212</v>
+        <v>1.0008</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>4.78</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2957,13 +2957,13 @@
         <v>0.18</v>
       </c>
       <c r="S23" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T23">
-        <v>0.2294</v>
+        <v>0.3293</v>
       </c>
       <c r="U23">
-        <v>0.2268</v>
+        <v>0.2155</v>
       </c>
       <c r="V23">
         <v>9</v>
@@ -2972,10 +2972,10 @@
         <v>0.2177</v>
       </c>
       <c r="X23">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y23">
-        <v>1.0344</v>
+        <v>1.0278</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2984,22 +2984,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>4.73</v>
+        <v>6.61</v>
       </c>
       <c r="AE23" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF23">
         <v>0.208</v>
       </c>
       <c r="AG23">
-        <v>1.0261</v>
+        <v>1.4436</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>4.73</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3058,13 +3058,13 @@
         <v>0.355</v>
       </c>
       <c r="S24" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T24">
-        <v>0.2174</v>
+        <v>0.2393</v>
       </c>
       <c r="U24">
-        <v>0.2326</v>
+        <v>0.2567</v>
       </c>
       <c r="V24">
         <v>9</v>
@@ -3073,10 +3073,10 @@
         <v>0.2467</v>
       </c>
       <c r="X24">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y24">
-        <v>1.0364</v>
+        <v>1.0819</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3085,7 +3085,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>4.86</v>
+        <v>5.47</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
@@ -3094,13 +3094,13 @@
         <v>0.2319</v>
       </c>
       <c r="AG24">
-        <v>0.9726</v>
+        <v>1.0493</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>4.86</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3159,13 +3159,13 @@
         <v>0.396</v>
       </c>
       <c r="S25" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T25">
-        <v>0.2689</v>
+        <v>0.3072</v>
       </c>
       <c r="U25">
-        <v>0.2599</v>
+        <v>0.2898</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -3174,10 +3174,10 @@
         <v>0.2557</v>
       </c>
       <c r="X25">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y25">
-        <v>1.0285</v>
+        <v>1.0952</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3186,22 +3186,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>6.27</v>
+        <v>7.48</v>
       </c>
       <c r="AE25" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="AF25">
         <v>0.214</v>
       </c>
       <c r="AG25">
-        <v>1.2027</v>
+        <v>1.3468</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="AM25">
-        <v>6.27</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3209,7 +3209,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C26">
         <v>3.5</v>
@@ -3260,25 +3260,25 @@
         <v>0.333</v>
       </c>
       <c r="S26" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2065</v>
+        <v>0.2064</v>
       </c>
       <c r="U26">
-        <v>0.2096</v>
+        <v>0.2092</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>0.2102</v>
       </c>
       <c r="X26">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y26">
-        <v>0.989</v>
+        <v>1.0004</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3287,7 +3287,7 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
@@ -3296,13 +3296,13 @@
         <v>0.1751</v>
       </c>
       <c r="AG26">
-        <v>0.9235</v>
+        <v>0.905</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3310,7 +3310,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27">
         <v>5.5</v>
@@ -3322,7 +3322,7 @@
         <v>-120</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G27">
         <v>823912</v>
@@ -3361,13 +3361,13 @@
         <v>0.344</v>
       </c>
       <c r="S27" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T27">
-        <v>0.2849</v>
+        <v>0.2262</v>
       </c>
       <c r="U27">
-        <v>0.2218</v>
+        <v>0.2126</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -3376,10 +3376,10 @@
         <v>0.2073</v>
       </c>
       <c r="X27">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y27">
-        <v>0.993</v>
+        <v>0.9497</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3388,7 +3388,7 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>8.06</v>
+        <v>6</v>
       </c>
       <c r="AE27" t="s">
         <v>49</v>
@@ -3397,13 +3397,13 @@
         <v>0.3242</v>
       </c>
       <c r="AG27">
-        <v>1.2743</v>
+        <v>0.9915</v>
       </c>
       <c r="AH27">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>7.24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3411,7 +3411,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28">
         <v>7.5</v>
@@ -3423,7 +3423,7 @@
         <v>-136</v>
       </c>
       <c r="F28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G28">
         <v>823912</v>
@@ -3462,13 +3462,13 @@
         <v>0.379</v>
       </c>
       <c r="S28" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="T28">
-        <v>0.2086</v>
+        <v>0.2874</v>
       </c>
       <c r="U28">
-        <v>0.2372</v>
+        <v>0.2323</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -3477,10 +3477,10 @@
         <v>0.2198</v>
       </c>
       <c r="X28">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y28">
-        <v>1.0017</v>
+        <v>0.9968</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3489,22 +3489,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>6.76</v>
+        <v>9.09</v>
       </c>
       <c r="AE28" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="AF28">
         <v>0.3109</v>
       </c>
       <c r="AG28">
-        <v>0.9329</v>
+        <v>1.2599</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="AM28">
-        <v>6.76</v>
+        <v>8.27</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3512,7 +3512,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29">
         <v>5.5</v>
@@ -3524,7 +3524,7 @@
         <v>-104</v>
       </c>
       <c r="F29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G29">
         <v>824156</v>
@@ -3563,7 +3563,7 @@
         <v>0.369</v>
       </c>
       <c r="S29" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="T29">
         <v>0.208</v>
@@ -3578,7 +3578,7 @@
         <v>0.2159</v>
       </c>
       <c r="X29">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y29">
         <v>0.9971</v>
@@ -3590,7 +3590,7 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>5.42</v>
+        <v>5.32</v>
       </c>
       <c r="AE29" t="s">
         <v>45</v>
@@ -3599,13 +3599,13 @@
         <v>0.2486</v>
       </c>
       <c r="AG29">
-        <v>0.9304</v>
+        <v>0.9119</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>5.42</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3625,7 +3625,7 @@
         <v>-102</v>
       </c>
       <c r="F30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G30">
         <v>824156</v>
@@ -3664,7 +3664,7 @@
         <v>0.367</v>
       </c>
       <c r="S30" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="T30">
         <v>0.2027</v>
@@ -3679,7 +3679,7 @@
         <v>0.2251</v>
       </c>
       <c r="X30">
-        <v>0.2236</v>
+        <v>0.2281</v>
       </c>
       <c r="Y30">
         <v>0.9948</v>
@@ -3691,7 +3691,7 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>4.98</v>
+        <v>4.88</v>
       </c>
       <c r="AE30" t="s">
         <v>45</v>
@@ -3700,13 +3700,13 @@
         <v>0.2462</v>
       </c>
       <c r="AG30">
-        <v>0.9066</v>
+        <v>0.8885</v>
       </c>
       <c r="AH30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>4.98</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3726,7 +3726,7 @@
         <v>-105</v>
       </c>
       <c r="F31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G31" t="s">
         <v>44</v>

--- a/data/k-props/2026-08-16.xlsx
+++ b/data/k-props/2026-08-16.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="94">
   <si>
     <t>date</t>
   </si>
@@ -160,111 +160,117 @@
     <t>Boston Red Sox @ Pittsburgh Pirates</t>
   </si>
   <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Lake Bachar</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Michael Soroka</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Bryce Elder</t>
+  </si>
+  <si>
+    <t>Ryan Weathers</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Dylan Cease</t>
+  </si>
+  <si>
+    <t>Jake Irvin</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ New York Mets</t>
+  </si>
+  <si>
+    <t>Christian Scott</t>
+  </si>
+  <si>
+    <t>Casey Mize</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Tanner Bibee</t>
+  </si>
+  <si>
+    <t>Sean Burke</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Drew Anderson</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Eury Pérez</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Nick Lodolo</t>
+  </si>
+  <si>
+    <t>Andrew Painter</t>
+  </si>
+  <si>
+    <t>Philadelphia Phillies @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Dean Kremer</t>
+  </si>
+  <si>
+    <t>Hunter Dobbins</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Edward Cabrera</t>
+  </si>
+  <si>
+    <t>Gabriel Hughes</t>
+  </si>
+  <si>
+    <t>Colorado Rockies @ San Francisco Giants</t>
+  </si>
+  <si>
+    <t>Blade Tidwell</t>
+  </si>
+  <si>
+    <t>Cody Bradford</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Athletics</t>
+  </si>
+  <si>
+    <t>Jacob Lopez</t>
+  </si>
+  <si>
+    <t>Noah Cameron</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Los Angeles Angels</t>
+  </si>
+  <si>
     <t>6-7</t>
   </si>
   <si>
-    <t>Lake Bachar</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Michael Soroka</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Bryce Elder</t>
-  </si>
-  <si>
-    <t>Ryan Weathers</t>
-  </si>
-  <si>
-    <t>New York Yankees @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>Dylan Cease</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Jake Irvin</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ New York Mets</t>
-  </si>
-  <si>
-    <t>Christian Scott</t>
-  </si>
-  <si>
-    <t>Casey Mize</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Tanner Bibee</t>
-  </si>
-  <si>
-    <t>Sean Burke</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>Drew Anderson</t>
-  </si>
-  <si>
-    <t>Eury Pérez</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Nick Lodolo</t>
-  </si>
-  <si>
-    <t>Andrew Painter</t>
-  </si>
-  <si>
-    <t>Philadelphia Phillies @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Dean Kremer</t>
-  </si>
-  <si>
-    <t>Hunter Dobbins</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Edward Cabrera</t>
-  </si>
-  <si>
-    <t>Gabriel Hughes</t>
-  </si>
-  <si>
-    <t>Colorado Rockies @ San Francisco Giants</t>
-  </si>
-  <si>
-    <t>Blade Tidwell</t>
-  </si>
-  <si>
-    <t>Jacob Lopez</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Athletics</t>
-  </si>
-  <si>
-    <t>Noah Cameron</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Los Angeles Angels</t>
-  </si>
-  <si>
     <t>Ryan Johnson</t>
   </si>
   <si>
@@ -283,16 +289,10 @@
     <t>Seattle Mariners @ Houston Astros</t>
   </si>
   <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
     <t>Hunter Brown</t>
   </si>
   <si>
     <t>Eury Perez</t>
-  </si>
-  <si>
-    <t>Cody Bradford</t>
   </si>
 </sst>
 </file>
@@ -866,10 +866,10 @@
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.1839</v>
+        <v>0.1849</v>
       </c>
       <c r="X2">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y2">
         <v>0.88</v>
@@ -881,7 +881,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -890,13 +890,13 @@
         <v>0.2245</v>
       </c>
       <c r="AG2">
-        <v>0.7059</v>
+        <v>0.7076</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -967,10 +967,10 @@
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2374</v>
+        <v>0.2372</v>
       </c>
       <c r="X3">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y3">
         <v>1.0287</v>
@@ -982,7 +982,7 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>5.35</v>
+        <v>5.37</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
@@ -991,13 +991,13 @@
         <v>0.2017</v>
       </c>
       <c r="AG3">
-        <v>1.1256</v>
+        <v>1.1283</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>5.35</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1026,7 +1026,7 @@
         <v>42</v>
       </c>
       <c r="I4">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1038,22 +1038,22 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>0.2129</v>
+        <v>0.2188</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="P4">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="Q4">
-        <v>0.2035</v>
+        <v>0.2119</v>
       </c>
       <c r="R4">
-        <v>0.361</v>
+        <v>0.371</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
@@ -1071,7 +1071,7 @@
         <v>0.2571</v>
       </c>
       <c r="X4">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y4">
         <v>1.1015</v>
@@ -1083,22 +1083,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>6.76</v>
+        <v>7.22</v>
       </c>
       <c r="AE4" t="s">
         <v>49</v>
       </c>
       <c r="AF4">
-        <v>0.2095</v>
+        <v>0.2162</v>
       </c>
       <c r="AG4">
-        <v>1.323</v>
+        <v>1.3262</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="AM4">
-        <v>6.76</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1163,7 +1163,7 @@
         <v>0.2177</v>
       </c>
       <c r="X5">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y5">
         <v>0.9171</v>
@@ -1175,7 +1175,7 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
@@ -1184,13 +1184,13 @@
         <v>0.2682</v>
       </c>
       <c r="AG5">
-        <v>0.9147</v>
+        <v>0.9169</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1231,22 +1231,22 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>0.2372</v>
+        <v>0.2347</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="P6">
         <v>4.08</v>
       </c>
       <c r="Q6">
-        <v>0.2472</v>
+        <v>0.2316</v>
       </c>
       <c r="R6">
-        <v>0.308</v>
+        <v>0.322</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
@@ -1261,10 +1261,10 @@
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.218</v>
+        <v>0.2177</v>
       </c>
       <c r="X6">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y6">
         <v>1.0284</v>
@@ -1276,22 +1276,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>5.52</v>
+        <v>5.44</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
       </c>
       <c r="AF6">
-        <v>0.2403</v>
+        <v>0.2337</v>
       </c>
       <c r="AG6">
-        <v>1.024</v>
+        <v>1.0264</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>5.52</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1332,22 +1332,22 @@
         <v>6</v>
       </c>
       <c r="M7">
-        <v>0.1927</v>
+        <v>0.1952</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="P7">
         <v>4.21</v>
       </c>
       <c r="Q7">
-        <v>0.1765</v>
+        <v>0.1885</v>
       </c>
       <c r="R7">
-        <v>0.373</v>
+        <v>0.379</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
@@ -1362,10 +1362,10 @@
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.1991</v>
+        <v>0.1993</v>
       </c>
       <c r="X7">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y7">
         <v>0.88</v>
@@ -1377,22 +1377,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
       </c>
       <c r="AF7">
-        <v>0.1867</v>
+        <v>0.1926</v>
       </c>
       <c r="AG7">
-        <v>0.8037</v>
+        <v>0.8056</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1421,7 +1421,7 @@
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1433,22 +1433,22 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>0.2569</v>
+        <v>0.2541</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="P8">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="Q8">
-        <v>0.2243</v>
+        <v>0.2101</v>
       </c>
       <c r="R8">
-        <v>0.349</v>
+        <v>0.373</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
@@ -1463,10 +1463,10 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>0.2108</v>
+        <v>0.2091</v>
       </c>
       <c r="X8">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y8">
         <v>0.9762</v>
@@ -1478,22 +1478,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.48</v>
+        <v>4.43</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.2456</v>
+        <v>0.2377</v>
       </c>
       <c r="AG8">
-        <v>0.8291</v>
+        <v>0.8311</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>4.48</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1522,7 +1522,7 @@
         <v>42</v>
       </c>
       <c r="I9">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1534,22 +1534,22 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>0.362</v>
+        <v>0.3635</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="P9">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="Q9">
-        <v>0.3583</v>
+        <v>0.3651</v>
       </c>
       <c r="R9">
-        <v>0.375</v>
+        <v>0.387</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
@@ -1564,10 +1564,10 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.244</v>
+        <v>0.2449</v>
       </c>
       <c r="X9">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y9">
         <v>1.0285</v>
@@ -1579,22 +1579,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>9.37</v>
+        <v>9.59</v>
       </c>
       <c r="AE9" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="AF9">
-        <v>0.3606</v>
+        <v>0.3641</v>
       </c>
       <c r="AG9">
-        <v>1.0623</v>
+        <v>1.0649</v>
       </c>
       <c r="AH9">
         <v>-0.82</v>
       </c>
       <c r="AM9">
-        <v>8.55</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1602,7 +1602,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10">
         <v>4.5</v>
@@ -1614,7 +1614,7 @@
         <v>-155</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>823590</v>
@@ -1623,7 +1623,7 @@
         <v>42</v>
       </c>
       <c r="I10">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1635,22 +1635,22 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>0.2328</v>
+        <v>0.23</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="P10">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="Q10">
-        <v>0.2111</v>
+        <v>0.2079</v>
       </c>
       <c r="R10">
-        <v>0.31</v>
+        <v>0.336</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
@@ -1665,10 +1665,10 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2247</v>
+        <v>0.225</v>
       </c>
       <c r="X10">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y10">
         <v>0.9461</v>
@@ -1680,22 +1680,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>4.65</v>
+        <v>4.71</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.2261</v>
+        <v>0.2226</v>
       </c>
       <c r="AG10">
-        <v>1.0693</v>
+        <v>1.0719</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>4.65</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1703,7 +1703,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11">
         <v>5.5</v>
@@ -1715,7 +1715,7 @@
         <v>115</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>823590</v>
@@ -1724,7 +1724,7 @@
         <v>42</v>
       </c>
       <c r="I11">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1736,22 +1736,22 @@
         <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2893</v>
+        <v>0.2861</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="P11">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="Q11">
-        <v>0.301</v>
+        <v>0.2895</v>
       </c>
       <c r="R11">
-        <v>0.34</v>
+        <v>0.363</v>
       </c>
       <c r="S11" t="s">
         <v>43</v>
@@ -1766,10 +1766,10 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2066</v>
+        <v>0.2076</v>
       </c>
       <c r="X11">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y11">
         <v>0.9898</v>
@@ -1781,22 +1781,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.31</v>
+        <v>5.38</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.2933</v>
+        <v>0.2873</v>
       </c>
       <c r="AG11">
-        <v>0.9255</v>
+        <v>0.9278</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.31</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1804,7 +1804,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1816,7 +1816,7 @@
         <v>-161</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>824397</v>
@@ -1825,7 +1825,7 @@
         <v>42</v>
       </c>
       <c r="I12">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1837,22 +1837,22 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>0.2377</v>
+        <v>0.2348</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="P12">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="Q12">
-        <v>0.1869</v>
+        <v>0.1739</v>
       </c>
       <c r="R12">
-        <v>0.349</v>
+        <v>0.315</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
@@ -1870,7 +1870,7 @@
         <v>0.2144</v>
       </c>
       <c r="X12">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y12">
         <v>0.88</v>
@@ -1882,22 +1882,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>3.43</v>
+        <v>3.27</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
       </c>
       <c r="AF12">
-        <v>0.22</v>
+        <v>0.2156</v>
       </c>
       <c r="AG12">
-        <v>0.825</v>
+        <v>0.827</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>3.43</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1905,7 +1905,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13">
         <v>4.5</v>
@@ -1917,7 +1917,7 @@
         <v>-113</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>824397</v>
@@ -1926,7 +1926,7 @@
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1938,22 +1938,22 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.1945</v>
+        <v>0.1903</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="P13">
-        <v>4.06</v>
+        <v>4.07</v>
       </c>
       <c r="Q13">
-        <v>0.2093</v>
+        <v>0.1897</v>
       </c>
       <c r="R13">
-        <v>0.392</v>
+        <v>0.367</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
@@ -1971,7 +1971,7 @@
         <v>0.2183</v>
       </c>
       <c r="X13">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y13">
         <v>1.0127</v>
@@ -1983,22 +1983,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>3.82</v>
+        <v>3.57</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.2003</v>
+        <v>0.1901</v>
       </c>
       <c r="AG13">
-        <v>0.8034</v>
+        <v>0.8053</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>3.82</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2006,7 +2006,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -2018,7 +2018,7 @@
         <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>824236</v>
@@ -2027,7 +2027,7 @@
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2039,22 +2039,22 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.2689</v>
+        <v>0.2697</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="P14">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="Q14">
-        <v>0.3028</v>
+        <v>0.3009</v>
       </c>
       <c r="R14">
-        <v>0.353</v>
+        <v>0.361</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
@@ -2069,10 +2069,10 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>0.2259</v>
+        <v>0.2248</v>
       </c>
       <c r="X14">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y14">
         <v>0.88</v>
@@ -2084,22 +2084,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>4.64</v>
+        <v>4.7</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.2808</v>
+        <v>0.281</v>
       </c>
       <c r="AG14">
-        <v>0.849</v>
+        <v>0.851</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>4.64</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2107,7 +2107,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2119,19 +2119,19 @@
         <v>-127</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G15">
         <v>824236</v>
       </c>
       <c r="H15" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
@@ -2140,22 +2140,22 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.264</v>
+        <v>0.2661</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="P15">
-        <v>4.27</v>
+        <v>4.28</v>
       </c>
       <c r="Q15">
-        <v>0.25</v>
+        <v>0.2593</v>
       </c>
       <c r="R15">
-        <v>0.275</v>
+        <v>0.288</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
@@ -2173,7 +2173,7 @@
         <v>0.2366</v>
       </c>
       <c r="X15">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y15">
         <v>1.0113</v>
@@ -2185,22 +2185,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.57</v>
+        <v>4.85</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.2601</v>
+        <v>0.2641</v>
       </c>
       <c r="AG15">
-        <v>1.057</v>
+        <v>1.0595</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>3.57</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2220,7 +2220,7 @@
         <v>42</v>
       </c>
       <c r="I16">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -2232,22 +2232,22 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0.2712</v>
+        <v>0.2692</v>
       </c>
       <c r="N16">
         <v>5</v>
       </c>
       <c r="O16">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="P16">
-        <v>4.01</v>
+        <v>4.03</v>
       </c>
       <c r="Q16">
-        <v>0.2411</v>
+        <v>0.2358</v>
       </c>
       <c r="R16">
-        <v>0.359</v>
+        <v>0.381</v>
       </c>
       <c r="S16" t="s">
         <v>43</v>
@@ -2262,10 +2262,10 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>0.2543</v>
+        <v>0.2542</v>
       </c>
       <c r="X16">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y16">
         <v>1.0914</v>
@@ -2277,22 +2277,22 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>7.69</v>
+        <v>7.76</v>
       </c>
       <c r="AE16" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="AF16">
-        <v>0.2604</v>
+        <v>0.2565</v>
       </c>
       <c r="AG16">
-        <v>1.2323</v>
+        <v>1.2353</v>
       </c>
       <c r="AH16">
         <v>-0.82</v>
       </c>
       <c r="AM16">
-        <v>6.87</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2321,7 +2321,7 @@
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2333,22 +2333,22 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>0.1821</v>
+        <v>0.1804</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="P17">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="Q17">
-        <v>0.1863</v>
+        <v>0.181</v>
       </c>
       <c r="R17">
-        <v>0.338</v>
+        <v>0.344</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
@@ -2363,10 +2363,10 @@
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2334</v>
+        <v>0.2314</v>
       </c>
       <c r="X17">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y17">
         <v>0.8813</v>
@@ -2378,22 +2378,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
       </c>
       <c r="AF17">
-        <v>0.1835</v>
+        <v>0.1806</v>
       </c>
       <c r="AG17">
-        <v>1.0512</v>
+        <v>1.0538</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2422,7 +2422,7 @@
         <v>42</v>
       </c>
       <c r="I18">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2434,22 +2434,22 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.1865</v>
+        <v>0.1854</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="P18">
         <v>4.49</v>
       </c>
       <c r="Q18">
-        <v>0.2235</v>
+        <v>0.2143</v>
       </c>
       <c r="R18">
-        <v>0.298</v>
+        <v>0.329</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2114</v>
+        <v>0.2113</v>
       </c>
       <c r="X18">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y18">
         <v>1</v>
@@ -2479,22 +2479,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>3.96</v>
+        <v>4.07</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
       </c>
       <c r="AF18">
-        <v>0.1975</v>
+        <v>0.1949</v>
       </c>
       <c r="AG18">
-        <v>0.986</v>
+        <v>0.9884</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>3.96</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2523,7 +2523,7 @@
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2535,22 +2535,22 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.2438</v>
+        <v>0.2442</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="P19">
-        <v>4.02</v>
+        <v>4.07</v>
       </c>
       <c r="Q19">
-        <v>0.2041</v>
+        <v>0.2105</v>
       </c>
       <c r="R19">
-        <v>0.329</v>
+        <v>0.363</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
@@ -2565,10 +2565,10 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2249</v>
+        <v>0.2246</v>
       </c>
       <c r="X19">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y19">
         <v>0.9041</v>
@@ -2580,22 +2580,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>3.37</v>
+        <v>3.67</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
       </c>
       <c r="AF19">
-        <v>0.2307</v>
+        <v>0.232</v>
       </c>
       <c r="AG19">
-        <v>0.8042</v>
+        <v>0.8062</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>3.37</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2624,7 +2624,7 @@
         <v>42</v>
       </c>
       <c r="I20">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2636,22 +2636,22 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.2199</v>
+        <v>0.2311</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P20">
         <v>4.24</v>
       </c>
       <c r="Q20">
-        <v>0.2105</v>
+        <v>0.2261</v>
       </c>
       <c r="R20">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
@@ -2669,7 +2669,7 @@
         <v>0.2172</v>
       </c>
       <c r="X20">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y20">
         <v>0.9429</v>
@@ -2681,22 +2681,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.77</v>
+        <v>5.04</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
       </c>
       <c r="AF20">
-        <v>0.2165</v>
+        <v>0.2293</v>
       </c>
       <c r="AG20">
-        <v>1.0659</v>
+        <v>1.0684</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>4.77</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2725,7 +2725,7 @@
         <v>42</v>
       </c>
       <c r="I21">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="b">
         <v>0</v>
@@ -2737,22 +2737,22 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.2104</v>
+        <v>0.2036</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="P21">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="Q21">
-        <v>0.2041</v>
+        <v>0.1961</v>
       </c>
       <c r="R21">
-        <v>0.329</v>
+        <v>0.338</v>
       </c>
       <c r="S21" t="s">
         <v>43</v>
@@ -2770,7 +2770,7 @@
         <v>0.2125</v>
       </c>
       <c r="X21">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y21">
         <v>0.915</v>
@@ -2782,22 +2782,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
       </c>
       <c r="AF21">
-        <v>0.2083</v>
+        <v>0.2011</v>
       </c>
       <c r="AG21">
-        <v>0.7717</v>
+        <v>0.7735</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2826,7 +2826,7 @@
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2838,22 +2838,22 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.2168</v>
+        <v>0.2012</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P22">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="Q22">
-        <v>0.213</v>
+        <v>0.1776</v>
       </c>
       <c r="R22">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
@@ -2871,7 +2871,7 @@
         <v>0.2015</v>
       </c>
       <c r="X22">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y22">
         <v>1.0015</v>
@@ -2883,22 +2883,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>4.69</v>
+        <v>4.18</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.2154</v>
+        <v>0.193</v>
       </c>
       <c r="AG22">
-        <v>1.0008</v>
+        <v>1.0032</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>4.69</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2927,7 +2927,7 @@
         <v>42</v>
       </c>
       <c r="I23">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2939,22 +2939,22 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2088</v>
+        <v>0.1818</v>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O23">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="P23">
-        <v>4.01</v>
+        <v>4.07</v>
       </c>
       <c r="Q23">
-        <v>0.2045</v>
+        <v>0.1587</v>
       </c>
       <c r="R23">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="S23" t="s">
         <v>43</v>
@@ -2972,7 +2972,7 @@
         <v>0.2177</v>
       </c>
       <c r="X23">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y23">
         <v>1.0278</v>
@@ -2984,22 +2984,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>6.61</v>
+        <v>5.34</v>
       </c>
       <c r="AE23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF23">
-        <v>0.208</v>
+        <v>0.1763</v>
       </c>
       <c r="AG23">
-        <v>1.4436</v>
+        <v>1.4471</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>6.61</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -3013,10 +3013,10 @@
         <v>4.5</v>
       </c>
       <c r="D24">
-        <v>-130</v>
+        <v>132</v>
       </c>
       <c r="E24">
-        <v>112</v>
+        <v>-148</v>
       </c>
       <c r="F24" t="s">
         <v>81</v>
@@ -3028,7 +3028,7 @@
         <v>42</v>
       </c>
       <c r="I24">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="b">
         <v>0</v>
@@ -3040,43 +3040,43 @@
         <v>6</v>
       </c>
       <c r="M24">
-        <v>0.2016</v>
+        <v>0.1538</v>
       </c>
       <c r="N24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O24">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="P24">
-        <v>4.54</v>
+        <v>4.24</v>
       </c>
       <c r="Q24">
-        <v>0.2909</v>
+        <v>0.1538</v>
       </c>
       <c r="R24">
-        <v>0.355</v>
+        <v>0.245</v>
       </c>
       <c r="S24" t="s">
         <v>43</v>
       </c>
       <c r="T24">
-        <v>0.2393</v>
+        <v>0.2222</v>
       </c>
       <c r="U24">
-        <v>0.2567</v>
+        <v>0.2017</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>0.2467</v>
+        <v>0.2486</v>
       </c>
       <c r="X24">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y24">
-        <v>1.0819</v>
+        <v>1.0855</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3085,22 +3085,22 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.47</v>
+        <v>3.53</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
       </c>
       <c r="AF24">
-        <v>0.2319</v>
+        <v>0.1538</v>
       </c>
       <c r="AG24">
-        <v>1.0493</v>
+        <v>0.9763</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>5.47</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3111,25 +3111,25 @@
         <v>82</v>
       </c>
       <c r="C25">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D25">
-        <v>-150</v>
+        <v>-130</v>
       </c>
       <c r="E25">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="F25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G25">
-        <v>823991</v>
+        <v>824965</v>
       </c>
       <c r="H25" t="s">
         <v>42</v>
       </c>
       <c r="I25">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="b">
         <v>0</v>
@@ -3141,43 +3141,43 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>0.2142</v>
+        <v>0.2041</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="P25">
-        <v>4.26</v>
+        <v>4.51</v>
       </c>
       <c r="Q25">
-        <v>0.2137</v>
+        <v>0.2818</v>
       </c>
       <c r="R25">
-        <v>0.396</v>
+        <v>0.355</v>
       </c>
       <c r="S25" t="s">
         <v>43</v>
       </c>
       <c r="T25">
-        <v>0.3072</v>
+        <v>0.2393</v>
       </c>
       <c r="U25">
-        <v>0.2898</v>
+        <v>0.2567</v>
       </c>
       <c r="V25">
         <v>9</v>
       </c>
       <c r="W25">
-        <v>0.2557</v>
+        <v>0.2467</v>
       </c>
       <c r="X25">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y25">
-        <v>1.0952</v>
+        <v>1.0819</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3186,22 +3186,22 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>7.48</v>
+        <v>5.45</v>
       </c>
       <c r="AE25" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="AF25">
-        <v>0.214</v>
+        <v>0.2317</v>
       </c>
       <c r="AG25">
-        <v>1.3468</v>
+        <v>1.0518</v>
       </c>
       <c r="AH25">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>6.66</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3209,19 +3209,19 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26">
+        <v>5.5</v>
+      </c>
+      <c r="D26">
+        <v>-150</v>
+      </c>
+      <c r="E26">
+        <v>128</v>
+      </c>
+      <c r="F26" t="s">
         <v>84</v>
-      </c>
-      <c r="C26">
-        <v>3.5</v>
-      </c>
-      <c r="D26">
-        <v>-154</v>
-      </c>
-      <c r="E26">
-        <v>131</v>
-      </c>
-      <c r="F26" t="s">
-        <v>83</v>
       </c>
       <c r="G26">
         <v>823991</v>
@@ -3230,7 +3230,7 @@
         <v>42</v>
       </c>
       <c r="I26">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3242,43 +3242,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1727</v>
+        <v>0.2123</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="P26">
-        <v>4.53</v>
+        <v>4.21</v>
       </c>
       <c r="Q26">
-        <v>0.18</v>
+        <v>0.1789</v>
       </c>
       <c r="R26">
-        <v>0.333</v>
+        <v>0.381</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2064</v>
+        <v>0.3072</v>
       </c>
       <c r="U26">
-        <v>0.2092</v>
+        <v>0.2898</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2102</v>
+        <v>0.2557</v>
       </c>
       <c r="X26">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y26">
-        <v>1.0004</v>
+        <v>1.0952</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3287,22 +3287,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>3.26</v>
+        <v>6.93</v>
       </c>
       <c r="AE26" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="AF26">
-        <v>0.1751</v>
+        <v>0.1996</v>
       </c>
       <c r="AG26">
-        <v>0.905</v>
+        <v>1.3501</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>3.26</v>
+        <v>6.93</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3310,28 +3310,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D27">
-        <v>108</v>
+        <v>-154</v>
       </c>
       <c r="E27">
-        <v>-120</v>
+        <v>131</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G27">
-        <v>823912</v>
+        <v>823991</v>
       </c>
       <c r="H27" t="s">
         <v>42</v>
       </c>
       <c r="I27">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3343,43 +3343,43 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.3194</v>
+        <v>0.1734</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P27">
-        <v>3.83</v>
+        <v>4.49</v>
       </c>
       <c r="Q27">
-        <v>0.3333</v>
+        <v>0.1667</v>
       </c>
       <c r="R27">
-        <v>0.344</v>
+        <v>0.338</v>
       </c>
       <c r="S27" t="s">
         <v>43</v>
       </c>
       <c r="T27">
-        <v>0.2262</v>
+        <v>0.2064</v>
       </c>
       <c r="U27">
-        <v>0.2126</v>
+        <v>0.2092</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2073</v>
+        <v>0.2102</v>
       </c>
       <c r="X27">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y27">
-        <v>0.9497</v>
+        <v>1.0004</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3388,22 +3388,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>6</v>
+        <v>3.22</v>
       </c>
       <c r="AE27" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF27">
-        <v>0.3242</v>
+        <v>0.1711</v>
       </c>
       <c r="AG27">
-        <v>0.9915</v>
+        <v>0.9072</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>6</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3414,16 +3414,16 @@
         <v>87</v>
       </c>
       <c r="C28">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D28">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E28">
-        <v>-136</v>
+        <v>-120</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G28">
         <v>823912</v>
@@ -3432,7 +3432,7 @@
         <v>42</v>
       </c>
       <c r="I28">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3444,43 +3444,43 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>0.3055</v>
+        <v>0.316</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="P28">
-        <v>3.89</v>
+        <v>3.81</v>
       </c>
       <c r="Q28">
-        <v>0.3197</v>
+        <v>0.3431</v>
       </c>
       <c r="R28">
-        <v>0.379</v>
+        <v>0.338</v>
       </c>
       <c r="S28" t="s">
         <v>43</v>
       </c>
       <c r="T28">
-        <v>0.2874</v>
+        <v>0.2262</v>
       </c>
       <c r="U28">
-        <v>0.2323</v>
+        <v>0.2126</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>0.2198</v>
+        <v>0.2073</v>
       </c>
       <c r="X28">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y28">
-        <v>0.9968</v>
+        <v>0.9497</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3489,22 +3489,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>9.09</v>
+        <v>5.91</v>
       </c>
       <c r="AE28" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="AF28">
-        <v>0.3109</v>
+        <v>0.3252</v>
       </c>
       <c r="AG28">
-        <v>1.2599</v>
+        <v>0.9939</v>
       </c>
       <c r="AH28">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>8.27</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3512,28 +3512,28 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29">
+        <v>7.5</v>
+      </c>
+      <c r="D29">
+        <v>110</v>
+      </c>
+      <c r="E29">
+        <v>-136</v>
+      </c>
+      <c r="F29" t="s">
         <v>88</v>
       </c>
-      <c r="C29">
-        <v>5.5</v>
-      </c>
-      <c r="D29">
-        <v>-110</v>
-      </c>
-      <c r="E29">
-        <v>-104</v>
-      </c>
-      <c r="F29" t="s">
-        <v>89</v>
-      </c>
       <c r="G29">
-        <v>824156</v>
+        <v>823912</v>
       </c>
       <c r="H29" t="s">
         <v>42</v>
       </c>
       <c r="I29">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3545,43 +3545,43 @@
         <v>6</v>
       </c>
       <c r="M29">
-        <v>0.244</v>
+        <v>0.298</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="P29">
-        <v>4.09</v>
+        <v>3.93</v>
       </c>
       <c r="Q29">
-        <v>0.2564</v>
+        <v>0.281</v>
       </c>
       <c r="R29">
-        <v>0.369</v>
+        <v>0.377</v>
       </c>
       <c r="S29" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="T29">
-        <v>0.208</v>
+        <v>0.2874</v>
       </c>
       <c r="U29">
-        <v>0.1979</v>
+        <v>0.2323</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>0.2159</v>
+        <v>0.2198</v>
       </c>
       <c r="X29">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y29">
-        <v>0.9971</v>
+        <v>0.9968</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3590,22 +3590,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>5.32</v>
+        <v>8.56</v>
       </c>
       <c r="AE29" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF29">
-        <v>0.2486</v>
+        <v>0.2916</v>
       </c>
       <c r="AG29">
-        <v>0.9119</v>
+        <v>1.263</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="AM29">
-        <v>5.32</v>
+        <v>7.74</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3613,19 +3613,19 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C30">
         <v>5.5</v>
       </c>
       <c r="D30">
-        <v>-111</v>
+        <v>-110</v>
       </c>
       <c r="E30">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="F30" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G30">
         <v>824156</v>
@@ -3634,7 +3634,7 @@
         <v>42</v>
       </c>
       <c r="I30">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3646,43 +3646,43 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>0.2491</v>
+        <v>0.244</v>
       </c>
       <c r="N30">
         <v>5</v>
       </c>
       <c r="O30">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P30">
-        <v>4.23</v>
+        <v>4.09</v>
       </c>
       <c r="Q30">
-        <v>0.2414</v>
+        <v>0.2564</v>
       </c>
       <c r="R30">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="S30" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="T30">
-        <v>0.2027</v>
+        <v>0.1629</v>
       </c>
       <c r="U30">
-        <v>0.1929</v>
+        <v>0.1725</v>
       </c>
       <c r="V30">
         <v>9</v>
       </c>
       <c r="W30">
-        <v>0.2251</v>
+        <v>0.2159</v>
       </c>
       <c r="X30">
-        <v>0.2281</v>
+        <v>0.2276</v>
       </c>
       <c r="Y30">
-        <v>0.9948</v>
+        <v>0.9454</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3691,22 +3691,22 @@
         <v>44</v>
       </c>
       <c r="AD30">
-        <v>4.88</v>
+        <v>3.96</v>
       </c>
       <c r="AE30" t="s">
         <v>45</v>
       </c>
       <c r="AF30">
-        <v>0.2462</v>
+        <v>0.2486</v>
       </c>
       <c r="AG30">
-        <v>0.8885</v>
+        <v>0.7158</v>
       </c>
       <c r="AH30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>4.88</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3717,31 +3717,73 @@
         <v>92</v>
       </c>
       <c r="C31">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D31">
         <v>-111</v>
       </c>
       <c r="E31">
-        <v>-105</v>
+        <v>-102</v>
       </c>
       <c r="F31" t="s">
-        <v>69</v>
-      </c>
-      <c r="G31" t="s">
-        <v>44</v>
+        <v>91</v>
+      </c>
+      <c r="G31">
+        <v>824156</v>
       </c>
       <c r="H31" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I31">
+        <v>5.3</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
       </c>
       <c r="L31">
         <v>6</v>
       </c>
+      <c r="M31">
+        <v>0.2491</v>
+      </c>
+      <c r="N31">
+        <v>5</v>
+      </c>
+      <c r="O31">
+        <v>116</v>
+      </c>
+      <c r="P31">
+        <v>4.23</v>
+      </c>
+      <c r="Q31">
+        <v>0.2414</v>
+      </c>
+      <c r="R31">
+        <v>0.367</v>
+      </c>
       <c r="S31" t="s">
-        <v>44</v>
-      </c>
-      <c r="V31" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T31">
+        <v>0.2313</v>
+      </c>
+      <c r="U31">
+        <v>0.1987</v>
+      </c>
+      <c r="V31">
+        <v>9</v>
+      </c>
+      <c r="W31">
+        <v>0.2251</v>
+      </c>
+      <c r="X31">
+        <v>0.2276</v>
+      </c>
+      <c r="Y31">
+        <v>1.006</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3749,8 +3791,23 @@
       <c r="AC31" t="s">
         <v>44</v>
       </c>
+      <c r="AD31">
+        <v>5.64</v>
+      </c>
       <c r="AE31" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AF31">
+        <v>0.2462</v>
+      </c>
+      <c r="AG31">
+        <v>1.0165</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>5.64</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3761,16 +3818,16 @@
         <v>93</v>
       </c>
       <c r="C32">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D32">
-        <v>132</v>
+        <v>-111</v>
       </c>
       <c r="E32">
-        <v>-148</v>
+        <v>-105</v>
       </c>
       <c r="F32" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="G32" t="s">
         <v>44</v>

--- a/data/k-props/2026-08-16.xlsx
+++ b/data/k-props/2026-08-16.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="98">
   <si>
     <t>date</t>
   </si>
@@ -145,28 +145,40 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Freddy Peralta</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Patrick Sandoval</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Lake Bachar</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Freddy Peralta</t>
-  </si>
-  <si>
-    <t>Patrick Sandoval</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Lake Bachar</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
   </si>
   <si>
     <t>Michael Soroka</t>
@@ -874,17 +886,23 @@
       <c r="Y2">
         <v>0.88</v>
       </c>
+      <c r="Z2">
+        <v>6</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>-1.28</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>3.22</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.2245</v>
@@ -894,6 +912,18 @@
       </c>
       <c r="AH2">
         <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>2.78</v>
+      </c>
+      <c r="AJ2">
+        <v>2.78</v>
+      </c>
+      <c r="AK2">
+        <v>2.78</v>
+      </c>
+      <c r="AL2">
+        <v>2.78</v>
       </c>
       <c r="AM2">
         <v>3.22</v>
@@ -904,7 +934,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>6.5</v>
@@ -975,17 +1005,23 @@
       <c r="Y3">
         <v>1.0287</v>
       </c>
+      <c r="Z3">
+        <v>2</v>
+      </c>
       <c r="AA3" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB3">
+        <v>-1.13</v>
       </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD3">
         <v>5.37</v>
       </c>
       <c r="AE3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>0.2017</v>
@@ -995,6 +1031,18 @@
       </c>
       <c r="AH3">
         <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>-3.37</v>
+      </c>
+      <c r="AJ3">
+        <v>3.37</v>
+      </c>
+      <c r="AK3">
+        <v>-3.37</v>
+      </c>
+      <c r="AL3">
+        <v>3.37</v>
       </c>
       <c r="AM3">
         <v>5.37</v>
@@ -1005,7 +1053,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>4.5</v>
@@ -1017,7 +1065,7 @@
         <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>823344</v>
@@ -1076,17 +1124,23 @@
       <c r="Y4">
         <v>1.1015</v>
       </c>
+      <c r="Z4">
+        <v>6</v>
+      </c>
       <c r="AA4" t="s">
         <v>44</v>
       </c>
+      <c r="AB4">
+        <v>1.9</v>
+      </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD4">
         <v>7.22</v>
       </c>
       <c r="AE4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AF4">
         <v>0.2162</v>
@@ -1096,6 +1150,18 @@
       </c>
       <c r="AH4">
         <v>-0.82</v>
+      </c>
+      <c r="AI4">
+        <v>-1.22</v>
+      </c>
+      <c r="AJ4">
+        <v>1.22</v>
+      </c>
+      <c r="AK4">
+        <v>-0.4</v>
+      </c>
+      <c r="AL4">
+        <v>0.4</v>
       </c>
       <c r="AM4">
         <v>6.4</v>
@@ -1106,16 +1172,16 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G5">
         <v>823344</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I5">
         <v>2.4</v>
@@ -1169,16 +1235,16 @@
         <v>0.9171</v>
       </c>
       <c r="AA5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD5">
         <v>2.22</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF5">
         <v>0.2682</v>
@@ -1198,7 +1264,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C6">
         <v>4.5</v>
@@ -1210,7 +1276,7 @@
         <v>-110</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>824880</v>
@@ -1269,17 +1335,23 @@
       <c r="Y6">
         <v>1.0284</v>
       </c>
+      <c r="Z6">
+        <v>5</v>
+      </c>
       <c r="AA6" t="s">
         <v>44</v>
       </c>
+      <c r="AB6">
+        <v>0.94</v>
+      </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD6">
         <v>5.44</v>
       </c>
       <c r="AE6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF6">
         <v>0.2337</v>
@@ -1289,6 +1361,18 @@
       </c>
       <c r="AH6">
         <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>-0.44</v>
+      </c>
+      <c r="AJ6">
+        <v>0.44</v>
+      </c>
+      <c r="AK6">
+        <v>-0.44</v>
+      </c>
+      <c r="AL6">
+        <v>0.44</v>
       </c>
       <c r="AM6">
         <v>5.44</v>
@@ -1299,7 +1383,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>3.5</v>
@@ -1311,7 +1395,7 @@
         <v>118</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>824880</v>
@@ -1370,17 +1454,23 @@
       <c r="Y7">
         <v>0.88</v>
       </c>
+      <c r="Z7">
+        <v>5</v>
+      </c>
       <c r="AA7" t="s">
         <v>44</v>
       </c>
+      <c r="AB7">
+        <v>-0.21</v>
+      </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD7">
         <v>3.29</v>
       </c>
       <c r="AE7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF7">
         <v>0.1926</v>
@@ -1390,6 +1480,18 @@
       </c>
       <c r="AH7">
         <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>1.71</v>
+      </c>
+      <c r="AJ7">
+        <v>1.71</v>
+      </c>
+      <c r="AK7">
+        <v>1.71</v>
+      </c>
+      <c r="AL7">
+        <v>1.71</v>
       </c>
       <c r="AM7">
         <v>3.29</v>
@@ -1400,7 +1502,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C8">
         <v>4.5</v>
@@ -1412,7 +1514,7 @@
         <v>125</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>822774</v>
@@ -1471,17 +1573,23 @@
       <c r="Y8">
         <v>0.9762</v>
       </c>
+      <c r="Z8">
+        <v>4</v>
+      </c>
       <c r="AA8" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB8">
+        <v>-0.07</v>
       </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD8">
         <v>4.43</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>0.2377</v>
@@ -1491,6 +1599,18 @@
       </c>
       <c r="AH8">
         <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>-0.43</v>
+      </c>
+      <c r="AJ8">
+        <v>0.43</v>
+      </c>
+      <c r="AK8">
+        <v>-0.43</v>
+      </c>
+      <c r="AL8">
+        <v>0.43</v>
       </c>
       <c r="AM8">
         <v>4.43</v>
@@ -1501,7 +1621,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C9">
         <v>8.5</v>
@@ -1513,7 +1633,7 @@
         <v>-110</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G9">
         <v>822774</v>
@@ -1572,17 +1692,23 @@
       <c r="Y9">
         <v>1.0285</v>
       </c>
+      <c r="Z9">
+        <v>10</v>
+      </c>
       <c r="AA9" t="s">
         <v>44</v>
       </c>
+      <c r="AB9">
+        <v>0.27</v>
+      </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD9">
         <v>9.59</v>
       </c>
       <c r="AE9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AF9">
         <v>0.3641</v>
@@ -1592,6 +1718,18 @@
       </c>
       <c r="AH9">
         <v>-0.82</v>
+      </c>
+      <c r="AI9">
+        <v>0.41</v>
+      </c>
+      <c r="AJ9">
+        <v>0.41</v>
+      </c>
+      <c r="AK9">
+        <v>1.23</v>
+      </c>
+      <c r="AL9">
+        <v>1.23</v>
       </c>
       <c r="AM9">
         <v>8.77</v>
@@ -1602,7 +1740,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>4.5</v>
@@ -1614,7 +1752,7 @@
         <v>-155</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G10">
         <v>823590</v>
@@ -1673,17 +1811,23 @@
       <c r="Y10">
         <v>0.9461</v>
       </c>
+      <c r="Z10">
+        <v>6</v>
+      </c>
       <c r="AA10" t="s">
         <v>44</v>
       </c>
+      <c r="AB10">
+        <v>0.21</v>
+      </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD10">
         <v>4.71</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF10">
         <v>0.2226</v>
@@ -1693,6 +1837,18 @@
       </c>
       <c r="AH10">
         <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>1.29</v>
+      </c>
+      <c r="AJ10">
+        <v>1.29</v>
+      </c>
+      <c r="AK10">
+        <v>1.29</v>
+      </c>
+      <c r="AL10">
+        <v>1.29</v>
       </c>
       <c r="AM10">
         <v>4.71</v>
@@ -1703,7 +1859,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C11">
         <v>5.5</v>
@@ -1715,7 +1871,7 @@
         <v>115</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>823590</v>
@@ -1774,17 +1930,23 @@
       <c r="Y11">
         <v>0.9898</v>
       </c>
+      <c r="Z11">
+        <v>7</v>
+      </c>
       <c r="AA11" t="s">
         <v>44</v>
       </c>
+      <c r="AB11">
+        <v>-0.12</v>
+      </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD11">
         <v>5.38</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF11">
         <v>0.2873</v>
@@ -1794,6 +1956,18 @@
       </c>
       <c r="AH11">
         <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>1.62</v>
+      </c>
+      <c r="AJ11">
+        <v>1.62</v>
+      </c>
+      <c r="AK11">
+        <v>1.62</v>
+      </c>
+      <c r="AL11">
+        <v>1.62</v>
       </c>
       <c r="AM11">
         <v>5.38</v>
@@ -1804,7 +1978,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1816,7 +1990,7 @@
         <v>-161</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>824397</v>
@@ -1875,17 +2049,23 @@
       <c r="Y12">
         <v>0.88</v>
       </c>
+      <c r="Z12">
+        <v>3</v>
+      </c>
       <c r="AA12" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB12">
+        <v>-1.23</v>
       </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD12">
         <v>3.27</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF12">
         <v>0.2156</v>
@@ -1895,6 +2075,18 @@
       </c>
       <c r="AH12">
         <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>-0.27</v>
+      </c>
+      <c r="AJ12">
+        <v>0.27</v>
+      </c>
+      <c r="AK12">
+        <v>-0.27</v>
+      </c>
+      <c r="AL12">
+        <v>0.27</v>
       </c>
       <c r="AM12">
         <v>3.27</v>
@@ -1905,7 +2097,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C13">
         <v>4.5</v>
@@ -1917,7 +2109,7 @@
         <v>-113</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>824397</v>
@@ -1976,17 +2168,23 @@
       <c r="Y13">
         <v>1.0127</v>
       </c>
+      <c r="Z13">
+        <v>3</v>
+      </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB13">
+        <v>-0.93</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD13">
         <v>3.57</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF13">
         <v>0.1901</v>
@@ -1996,6 +2194,18 @@
       </c>
       <c r="AH13">
         <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>-0.57</v>
+      </c>
+      <c r="AJ13">
+        <v>0.57</v>
+      </c>
+      <c r="AK13">
+        <v>-0.57</v>
+      </c>
+      <c r="AL13">
+        <v>0.57</v>
       </c>
       <c r="AM13">
         <v>3.57</v>
@@ -2006,7 +2216,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C14">
         <v>5.5</v>
@@ -2018,7 +2228,7 @@
         <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G14">
         <v>824236</v>
@@ -2077,17 +2287,23 @@
       <c r="Y14">
         <v>0.88</v>
       </c>
+      <c r="Z14">
+        <v>2</v>
+      </c>
       <c r="AA14" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB14">
+        <v>-0.8</v>
       </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD14">
         <v>4.7</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF14">
         <v>0.281</v>
@@ -2097,6 +2313,18 @@
       </c>
       <c r="AH14">
         <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>-2.7</v>
+      </c>
+      <c r="AJ14">
+        <v>2.7</v>
+      </c>
+      <c r="AK14">
+        <v>-2.7</v>
+      </c>
+      <c r="AL14">
+        <v>2.7</v>
       </c>
       <c r="AM14">
         <v>4.7</v>
@@ -2107,7 +2335,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2119,13 +2347,13 @@
         <v>-127</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G15">
         <v>824236</v>
       </c>
       <c r="H15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I15">
         <v>4</v>
@@ -2178,17 +2406,23 @@
       <c r="Y15">
         <v>1.0113</v>
       </c>
+      <c r="Z15">
+        <v>5</v>
+      </c>
       <c r="AA15" t="s">
         <v>44</v>
       </c>
+      <c r="AB15">
+        <v>0.35</v>
+      </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD15">
         <v>4.85</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF15">
         <v>0.2641</v>
@@ -2198,6 +2432,18 @@
       </c>
       <c r="AH15">
         <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>0.15</v>
+      </c>
+      <c r="AJ15">
+        <v>0.15</v>
+      </c>
+      <c r="AK15">
+        <v>0.15</v>
+      </c>
+      <c r="AL15">
+        <v>0.15</v>
       </c>
       <c r="AM15">
         <v>4.85</v>
@@ -2208,10 +2454,10 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G16">
         <v>824477</v>
@@ -2271,16 +2517,16 @@
         <v>1.0914</v>
       </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD16">
         <v>7.76</v>
       </c>
       <c r="AE16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AF16">
         <v>0.2565</v>
@@ -2300,7 +2546,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2312,7 +2558,7 @@
         <v>100</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G17">
         <v>824477</v>
@@ -2371,17 +2617,23 @@
       <c r="Y17">
         <v>0.8813</v>
       </c>
+      <c r="Z17">
+        <v>2</v>
+      </c>
       <c r="AA17" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB17">
+        <v>-0.71</v>
       </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD17">
         <v>3.79</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF17">
         <v>0.1806</v>
@@ -2391,6 +2643,18 @@
       </c>
       <c r="AH17">
         <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>-1.79</v>
+      </c>
+      <c r="AJ17">
+        <v>1.79</v>
+      </c>
+      <c r="AK17">
+        <v>-1.79</v>
+      </c>
+      <c r="AL17">
+        <v>1.79</v>
       </c>
       <c r="AM17">
         <v>3.79</v>
@@ -2401,7 +2665,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C18">
         <v>3.5</v>
@@ -2413,7 +2677,7 @@
         <v>110</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G18">
         <v>823670</v>
@@ -2472,17 +2736,23 @@
       <c r="Y18">
         <v>1</v>
       </c>
+      <c r="Z18">
+        <v>2</v>
+      </c>
       <c r="AA18" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB18">
+        <v>0.57</v>
       </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD18">
         <v>4.07</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF18">
         <v>0.1949</v>
@@ -2492,6 +2762,18 @@
       </c>
       <c r="AH18">
         <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>-2.07</v>
+      </c>
+      <c r="AJ18">
+        <v>2.07</v>
+      </c>
+      <c r="AK18">
+        <v>-2.07</v>
+      </c>
+      <c r="AL18">
+        <v>2.07</v>
       </c>
       <c r="AM18">
         <v>4.07</v>
@@ -2502,7 +2784,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C19">
         <v>4.5</v>
@@ -2514,7 +2796,7 @@
         <v>-132</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G19">
         <v>823670</v>
@@ -2573,17 +2855,23 @@
       <c r="Y19">
         <v>0.9041</v>
       </c>
+      <c r="Z19">
+        <v>6</v>
+      </c>
       <c r="AA19" t="s">
         <v>44</v>
       </c>
+      <c r="AB19">
+        <v>-0.83</v>
+      </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD19">
         <v>3.67</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>0.232</v>
@@ -2593,6 +2881,18 @@
       </c>
       <c r="AH19">
         <v>0</v>
+      </c>
+      <c r="AI19">
+        <v>2.33</v>
+      </c>
+      <c r="AJ19">
+        <v>2.33</v>
+      </c>
+      <c r="AK19">
+        <v>2.33</v>
+      </c>
+      <c r="AL19">
+        <v>2.33</v>
       </c>
       <c r="AM19">
         <v>3.67</v>
@@ -2603,7 +2903,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C20">
         <v>3.5</v>
@@ -2615,7 +2915,7 @@
         <v>110</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G20">
         <v>824642</v>
@@ -2674,17 +2974,23 @@
       <c r="Y20">
         <v>0.9429</v>
       </c>
+      <c r="Z20">
+        <v>7</v>
+      </c>
       <c r="AA20" t="s">
         <v>44</v>
       </c>
+      <c r="AB20">
+        <v>1.54</v>
+      </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD20">
         <v>5.04</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF20">
         <v>0.2293</v>
@@ -2694,6 +3000,18 @@
       </c>
       <c r="AH20">
         <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>1.96</v>
+      </c>
+      <c r="AJ20">
+        <v>1.96</v>
+      </c>
+      <c r="AK20">
+        <v>1.96</v>
+      </c>
+      <c r="AL20">
+        <v>1.96</v>
       </c>
       <c r="AM20">
         <v>5.04</v>
@@ -2704,7 +3022,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C21">
         <v>4.5</v>
@@ -2716,7 +3034,7 @@
         <v>-158</v>
       </c>
       <c r="F21" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G21">
         <v>824642</v>
@@ -2775,17 +3093,23 @@
       <c r="Y21">
         <v>0.915</v>
       </c>
+      <c r="Z21">
+        <v>2</v>
+      </c>
       <c r="AA21" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB21">
+        <v>-1.38</v>
       </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD21">
         <v>3.12</v>
       </c>
       <c r="AE21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF21">
         <v>0.2011</v>
@@ -2795,6 +3119,18 @@
       </c>
       <c r="AH21">
         <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>-1.12</v>
+      </c>
+      <c r="AJ21">
+        <v>1.12</v>
+      </c>
+      <c r="AK21">
+        <v>-1.12</v>
+      </c>
+      <c r="AL21">
+        <v>1.12</v>
       </c>
       <c r="AM21">
         <v>3.12</v>
@@ -2805,7 +3141,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C22">
         <v>3.5</v>
@@ -2817,7 +3153,7 @@
         <v>129</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G22">
         <v>823182</v>
@@ -2876,17 +3212,23 @@
       <c r="Y22">
         <v>1.0015</v>
       </c>
+      <c r="Z22">
+        <v>2</v>
+      </c>
       <c r="AA22" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB22">
+        <v>0.68</v>
       </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD22">
         <v>4.18</v>
       </c>
       <c r="AE22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF22">
         <v>0.193</v>
@@ -2896,6 +3238,18 @@
       </c>
       <c r="AH22">
         <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>-2.18</v>
+      </c>
+      <c r="AJ22">
+        <v>2.18</v>
+      </c>
+      <c r="AK22">
+        <v>-2.18</v>
+      </c>
+      <c r="AL22">
+        <v>2.18</v>
       </c>
       <c r="AM22">
         <v>4.18</v>
@@ -2906,7 +3260,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C23">
         <v>4.5</v>
@@ -2918,7 +3272,7 @@
         <v>-105</v>
       </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G23">
         <v>823182</v>
@@ -2977,17 +3331,23 @@
       <c r="Y23">
         <v>1.0278</v>
       </c>
+      <c r="Z23">
+        <v>1</v>
+      </c>
       <c r="AA23" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB23">
+        <v>0.84</v>
       </c>
       <c r="AC23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD23">
         <v>5.34</v>
       </c>
       <c r="AE23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF23">
         <v>0.1763</v>
@@ -2997,6 +3357,18 @@
       </c>
       <c r="AH23">
         <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>-4.34</v>
+      </c>
+      <c r="AJ23">
+        <v>4.34</v>
+      </c>
+      <c r="AK23">
+        <v>-4.34</v>
+      </c>
+      <c r="AL23">
+        <v>4.34</v>
       </c>
       <c r="AM23">
         <v>5.34</v>
@@ -3007,7 +3379,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C24">
         <v>4.5</v>
@@ -3019,7 +3391,7 @@
         <v>-148</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G24">
         <v>824965</v>
@@ -3078,17 +3450,23 @@
       <c r="Y24">
         <v>1.0855</v>
       </c>
+      <c r="Z24">
+        <v>4</v>
+      </c>
       <c r="AA24" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB24">
+        <v>-0.97</v>
       </c>
       <c r="AC24" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD24">
         <v>3.53</v>
       </c>
       <c r="AE24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF24">
         <v>0.1538</v>
@@ -3098,6 +3476,18 @@
       </c>
       <c r="AH24">
         <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0.47</v>
+      </c>
+      <c r="AJ24">
+        <v>0.47</v>
+      </c>
+      <c r="AK24">
+        <v>0.47</v>
+      </c>
+      <c r="AL24">
+        <v>0.47</v>
       </c>
       <c r="AM24">
         <v>3.53</v>
@@ -3108,7 +3498,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C25">
         <v>4.5</v>
@@ -3120,7 +3510,7 @@
         <v>112</v>
       </c>
       <c r="F25" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G25">
         <v>824965</v>
@@ -3179,17 +3569,23 @@
       <c r="Y25">
         <v>1.0819</v>
       </c>
+      <c r="Z25">
+        <v>6</v>
+      </c>
       <c r="AA25" t="s">
         <v>44</v>
       </c>
+      <c r="AB25">
+        <v>0.95</v>
+      </c>
       <c r="AC25" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD25">
         <v>5.45</v>
       </c>
       <c r="AE25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF25">
         <v>0.2317</v>
@@ -3199,6 +3595,18 @@
       </c>
       <c r="AH25">
         <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0.55</v>
+      </c>
+      <c r="AJ25">
+        <v>0.55</v>
+      </c>
+      <c r="AK25">
+        <v>0.55</v>
+      </c>
+      <c r="AL25">
+        <v>0.55</v>
       </c>
       <c r="AM25">
         <v>5.45</v>
@@ -3209,7 +3617,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C26">
         <v>5.5</v>
@@ -3221,7 +3629,7 @@
         <v>128</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G26">
         <v>823991</v>
@@ -3280,17 +3688,23 @@
       <c r="Y26">
         <v>1.0952</v>
       </c>
+      <c r="Z26">
+        <v>8</v>
+      </c>
       <c r="AA26" t="s">
         <v>44</v>
       </c>
+      <c r="AB26">
+        <v>1.43</v>
+      </c>
       <c r="AC26" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD26">
         <v>6.93</v>
       </c>
       <c r="AE26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AF26">
         <v>0.1996</v>
@@ -3300,6 +3714,18 @@
       </c>
       <c r="AH26">
         <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>1.07</v>
+      </c>
+      <c r="AJ26">
+        <v>1.07</v>
+      </c>
+      <c r="AK26">
+        <v>1.07</v>
+      </c>
+      <c r="AL26">
+        <v>1.07</v>
       </c>
       <c r="AM26">
         <v>6.93</v>
@@ -3310,7 +3736,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C27">
         <v>3.5</v>
@@ -3322,7 +3748,7 @@
         <v>131</v>
       </c>
       <c r="F27" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G27">
         <v>823991</v>
@@ -3381,17 +3807,23 @@
       <c r="Y27">
         <v>1.0004</v>
       </c>
+      <c r="Z27">
+        <v>4</v>
+      </c>
       <c r="AA27" t="s">
         <v>44</v>
       </c>
+      <c r="AB27">
+        <v>-0.28</v>
+      </c>
       <c r="AC27" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD27">
         <v>3.22</v>
       </c>
       <c r="AE27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF27">
         <v>0.1711</v>
@@ -3401,6 +3833,18 @@
       </c>
       <c r="AH27">
         <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0.78</v>
+      </c>
+      <c r="AJ27">
+        <v>0.78</v>
+      </c>
+      <c r="AK27">
+        <v>0.78</v>
+      </c>
+      <c r="AL27">
+        <v>0.78</v>
       </c>
       <c r="AM27">
         <v>3.22</v>
@@ -3411,7 +3855,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C28">
         <v>5.5</v>
@@ -3423,7 +3867,7 @@
         <v>-120</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G28">
         <v>823912</v>
@@ -3482,17 +3926,23 @@
       <c r="Y28">
         <v>0.9497</v>
       </c>
+      <c r="Z28">
+        <v>6</v>
+      </c>
       <c r="AA28" t="s">
         <v>44</v>
       </c>
+      <c r="AB28">
+        <v>0.41</v>
+      </c>
       <c r="AC28" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD28">
         <v>5.91</v>
       </c>
       <c r="AE28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF28">
         <v>0.3252</v>
@@ -3502,6 +3952,18 @@
       </c>
       <c r="AH28">
         <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0.09</v>
+      </c>
+      <c r="AJ28">
+        <v>0.09</v>
+      </c>
+      <c r="AK28">
+        <v>0.09</v>
+      </c>
+      <c r="AL28">
+        <v>0.09</v>
       </c>
       <c r="AM28">
         <v>5.91</v>
@@ -3512,7 +3974,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C29">
         <v>7.5</v>
@@ -3524,7 +3986,7 @@
         <v>-136</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G29">
         <v>823912</v>
@@ -3583,17 +4045,23 @@
       <c r="Y29">
         <v>0.9968</v>
       </c>
+      <c r="Z29">
+        <v>7</v>
+      </c>
       <c r="AA29" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB29">
+        <v>0.24</v>
       </c>
       <c r="AC29" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD29">
         <v>8.56</v>
       </c>
       <c r="AE29" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AF29">
         <v>0.2916</v>
@@ -3603,6 +4071,18 @@
       </c>
       <c r="AH29">
         <v>-0.82</v>
+      </c>
+      <c r="AI29">
+        <v>-1.56</v>
+      </c>
+      <c r="AJ29">
+        <v>1.56</v>
+      </c>
+      <c r="AK29">
+        <v>-0.74</v>
+      </c>
+      <c r="AL29">
+        <v>0.74</v>
       </c>
       <c r="AM29">
         <v>7.74</v>
@@ -3613,7 +4093,7 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C30">
         <v>5.5</v>
@@ -3625,7 +4105,7 @@
         <v>-104</v>
       </c>
       <c r="F30" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G30">
         <v>824156</v>
@@ -3684,17 +4164,23 @@
       <c r="Y30">
         <v>0.9454</v>
       </c>
+      <c r="Z30">
+        <v>4</v>
+      </c>
       <c r="AA30" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB30">
+        <v>-1.54</v>
       </c>
       <c r="AC30" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="AD30">
         <v>3.96</v>
       </c>
       <c r="AE30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF30">
         <v>0.2486</v>
@@ -3704,6 +4190,18 @@
       </c>
       <c r="AH30">
         <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0.04</v>
+      </c>
+      <c r="AJ30">
+        <v>0.04</v>
+      </c>
+      <c r="AK30">
+        <v>0.04</v>
+      </c>
+      <c r="AL30">
+        <v>0.04</v>
       </c>
       <c r="AM30">
         <v>3.96</v>
@@ -3714,7 +4212,7 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C31">
         <v>5.5</v>
@@ -3726,7 +4224,7 @@
         <v>-102</v>
       </c>
       <c r="F31" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G31">
         <v>824156</v>
@@ -3785,17 +4283,23 @@
       <c r="Y31">
         <v>1.006</v>
       </c>
+      <c r="Z31">
+        <v>5</v>
+      </c>
       <c r="AA31" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB31">
+        <v>0.14</v>
       </c>
       <c r="AC31" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AD31">
         <v>5.64</v>
       </c>
       <c r="AE31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF31">
         <v>0.2462</v>
@@ -3805,6 +4309,18 @@
       </c>
       <c r="AH31">
         <v>0</v>
+      </c>
+      <c r="AI31">
+        <v>-0.64</v>
+      </c>
+      <c r="AJ31">
+        <v>0.64</v>
+      </c>
+      <c r="AK31">
+        <v>-0.64</v>
+      </c>
+      <c r="AL31">
+        <v>0.64</v>
       </c>
       <c r="AM31">
         <v>5.64</v>
@@ -3815,7 +4331,7 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C32">
         <v>6.5</v>
@@ -3827,31 +4343,31 @@
         <v>-105</v>
       </c>
       <c r="F32" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G32" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="L32">
         <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="V32" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AA32" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AC32" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AE32" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
